--- a/DOSSIES_MULTIFORMATO/SEJUSC/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEJUSC/dossie.xlsx
@@ -636,21 +636,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2018NE00188</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7/2016</t>
-        </is>
-      </c>
+          <t>2018NE00510</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>31/08/2018</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43648.48</v>
+        <v>4775.48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -659,24 +655,28 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6º TERMO ADITIVO AO CONTRATO Nº 07/2018 Contratação de empresa especializada em prestação de serviços de firewall, prodam Rh, internet, link e gestor de conteúdo.</t>
+          <t>REFORÇO NE 114 CT. 002/2016 - CRONOGRAMA: SETEMBRO A DEZEMBRO/18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2018NE00510</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>2018NE00188</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7/2016</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>31/08/2018</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4775.48</v>
+        <v>43648.48</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>REFORÇO NE 114 CT. 002/2016 - CRONOGRAMA: SETEMBRO A DEZEMBRO/18</t>
+          <t>6º TERMO ADITIVO AO CONTRATO Nº 07/2018 Contratação de empresa especializada em prestação de serviços de firewall, prodam Rh, internet, link e gestor de conteúdo.</t>
         </is>
       </c>
     </row>
@@ -722,10 +722,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2019NE00080</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>2019NE00079</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>31/01/2019</t>
@@ -741,19 +745,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>anulação por equivoco na descrição.</t>
+          <t>3º TERMO ADITIVO AO CONTRATO Nº 002/2016-SEJUSC. OBJETO: PRORROGAÇÃO DO PRAZO DE VIGÊNCIA DO CONTRATO ORIGINAL DE PRESTAÇÃO DE EXECUÇÃO DE SISTEMAS SPROWEB, POR MAIS 12(DOZE) MESES, CFE CLÁUSULA OITAV</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2019NE00082</t>
+          <t>2019NE00081</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -762,7 +766,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2568</v>
+        <v>3570.76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -771,19 +775,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO Nº 002/2016-SEJUSC OBJETO: PRORROGAÇÃO DO PRAZO DE VIGÊNCIA DO CONTRATO ORIGINAL DE PRESTAÇÃO DE EXECUÇÃO DE SISTEMAS SPROWEB, POR MAIS 12(DOZE) MESES, CFE CLÁUSULA OITAVA</t>
+          <t>EMPENHO REF. CRONOGRAMA FEVEREIRO E MARÇO/19, 3º TERMO ADITIVO, CT. 001/2016-SERVIÇO PREST. INFORMATICA EM GERAL, VIGÊNCIA: 31/01/2019 A 31/01/2020.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2019NE00081</t>
+          <t>2019NE00082</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -792,7 +796,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3570.76</v>
+        <v>2568</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -801,21 +805,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EMPENHO REF. CRONOGRAMA FEVEREIRO E MARÇO/19, 3º TERMO ADITIVO, CT. 001/2016-SERVIÇO PREST. INFORMATICA EM GERAL, VIGÊNCIA: 31/01/2019 A 31/01/2020.</t>
+          <t>3º TERMO ADITIVO AO CONTRATO Nº 002/2016-SEJUSC OBJETO: PRORROGAÇÃO DO PRAZO DE VIGÊNCIA DO CONTRATO ORIGINAL DE PRESTAÇÃO DE EXECUÇÃO DE SISTEMAS SPROWEB, POR MAIS 12(DOZE) MESES, CFE CLÁUSULA OITAVA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2019NE00079</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2019NE00080</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>31/01/2019</t>
@@ -831,19 +831,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO Nº 002/2016-SEJUSC. OBJETO: PRORROGAÇÃO DO PRAZO DE VIGÊNCIA DO CONTRATO ORIGINAL DE PRESTAÇÃO DE EXECUÇÃO DE SISTEMAS SPROWEB, POR MAIS 12(DOZE) MESES, CFE CLÁUSULA OITAV</t>
+          <t>anulação por equivoco na descrição.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021NE0000739</t>
+          <t>2021NE0000738</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2308.04</v>
+        <v>4882.47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -861,19 +861,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CT 07/21</t>
+          <t>CT 3/17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021NE0000738</t>
+          <t>2021NE0000739</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4882.47</v>
+        <v>2308.04</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CT 3/17</t>
+          <t>CT 07/21</t>
         </is>
       </c>
     </row>
@@ -928,17 +928,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2020NE00340</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>2020NE00341</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>34/2016</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>30/07/2020</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8756.559999999999</v>
+        <v>7281.27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -947,28 +951,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anulação de empenho para ajustes na descrição e valor empenhado.</t>
+          <t>4º T.A AO CONTRATO N° 034/2016-SEJUSC - PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 (DOZE) MESES, REFERENTE AOS SERVIÇOS DE LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO GESTOR DE CONTEÚDO WEB.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020NE00341</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>34/2016</t>
-        </is>
-      </c>
+          <t>2020NE00340</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>30/07/2020</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7281.27</v>
+        <v>8756.559999999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -977,19 +977,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4º T.A AO CONTRATO N° 034/2016-SEJUSC - PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 (DOZE) MESES, REFERENTE AOS SERVIÇOS DE LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO GESTOR DE CONTEÚDO WEB.</t>
+          <t>Anulação de empenho para ajustes na descrição e valor empenhado.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2016NE00173</t>
+          <t>2016NE00174</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3/2011</t>
+          <t>10/2011</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19944.86</v>
+        <v>1098.33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Contratação de prestação de Serviço de acesso à rede mundial de computadores (Internet), conforme discriminação em projeto básico.</t>
+          <t>Contratação de prestação de serviços de hospedagem de site institucional dessa SEPED</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2016NE00174</t>
+          <t>2016NE00173</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10/2011</t>
+          <t>3/2011</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1098.33</v>
+        <v>19944.86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviços de hospedagem de site institucional dessa SEPED</t>
+          <t>Contratação de prestação de Serviço de acesso à rede mundial de computadores (Internet), conforme discriminação em projeto básico.</t>
         </is>
       </c>
     </row>
@@ -1104,21 +1104,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2015NE00116</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3/2011</t>
-        </is>
-      </c>
+          <t>2015NE00474</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>30/04/2015</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>49862.05</v>
+        <v>6826.08</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1127,19 +1123,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015 - Supressão</t>
+          <t>Referente a Serviços de Processo de Dados LINK (INTERNET), no mês Abril/2015.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2015NE00118</t>
+          <t>2015NE00117</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10/2011</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1148,7 +1144,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2928.9</v>
+        <v>4063.68</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1164,17 +1160,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2015NE00474</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>2015NE00118</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10/2011</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>30/04/2015</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6826.08</v>
+        <v>2928.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1183,19 +1183,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Referente a Serviços de Processo de Dados LINK (INTERNET), no mês Abril/2015.</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2015NE00117</t>
+          <t>2015NE00116</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>3/2011</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4063.68</v>
+        <v>49862.05</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1213,14 +1213,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>Cobertura Financeira 2015 - Supressão</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2016NE00185</t>
+          <t>2016NE00191</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1243,14 +1243,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES ABRIL/2015. CT 05/2013</t>
+          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES NOVEMBRO/2015. CT 05/2013</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2016NE00190</t>
+          <t>2016NE00188</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1273,14 +1273,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES OUTUBRO/2015. CT 05/2013</t>
+          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES AGOSTO/2015. CT 05/2013</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2016NE00187</t>
+          <t>2016NE00189</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES JULHO/2015. CT 05/2013</t>
+          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES SETEMBRO/2015. CT 05/2013</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2016NE00192</t>
+          <t>2016NE00186</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1333,14 +1333,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES DEZEMBRO/2015. CT 05/2013</t>
+          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES MAIO/2015. CT 05/2013</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2016NE00186</t>
+          <t>2016NE00192</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1363,14 +1363,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES MAIO/2015. CT 05/2013</t>
+          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES DEZEMBRO/2015. CT 05/2013</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2016NE00189</t>
+          <t>2016NE00187</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1393,14 +1393,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES SETEMBRO/2015. CT 05/2013</t>
+          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES JULHO/2015. CT 05/2013</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2016NE00188</t>
+          <t>2016NE00190</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1423,14 +1423,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES AGOSTO/2015. CT 05/2013</t>
+          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES OUTUBRO/2015. CT 05/2013</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2016NE00191</t>
+          <t>2016NE00185</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1453,14 +1453,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES NOVEMBRO/2015. CT 05/2013</t>
+          <t>RECONHECIMENTO DE DÍVIDA REF A PRESTAÇÃO DE SERVIÇOS DE ACESSO REMOTO E FIREWALL NA SEDE DA SEJUSC, NO MES ABRIL/2015. CT 05/2013</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2015NE00406</t>
+          <t>2015NE00384</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14623.1</v>
+        <v>8540.879999999999</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 137/2015. Ref. ao pagamento da NFS-e nº 13911, emitidas em 18/03/2015, com o devido atesto, disponibilidade de uso de recursos, Sist. Penitenci</t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 124/2015. Serviços de acesso à rede internet/computador central, durante o mês de Dezembro/14, conforme NFS-e 13648, de 24/02/2015, devidame</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2015NE00383</t>
+          <t>2015NE00404</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8540.879999999999</v>
+        <v>14623.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1505,14 +1505,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 123/2015. Serviços de acesso à rede internet/computador central, durante o mês de Novembro/14, conforme NFS-e 13647, de 24/02/2015, devidame</t>
+          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 136/2015. Ref. ao pagamento da NFS-e nº 13910, emitidas em 18/03/2015, com o devido atesto, disponibilidade de uso de recursos, Sist. Penitenci</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2015NE00404</t>
+          <t>2015NE00383</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14623.1</v>
+        <v>8540.879999999999</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1531,14 +1531,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 136/2015. Ref. ao pagamento da NFS-e nº 13910, emitidas em 18/03/2015, com o devido atesto, disponibilidade de uso de recursos, Sist. Penitenci</t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 123/2015. Serviços de acesso à rede internet/computador central, durante o mês de Novembro/14, conforme NFS-e 13647, de 24/02/2015, devidame</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2015NE00384</t>
+          <t>2015NE00406</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8540.879999999999</v>
+        <v>14623.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1557,19 +1557,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 124/2015. Serviços de acesso à rede internet/computador central, durante o mês de Dezembro/14, conforme NFS-e 13648, de 24/02/2015, devidame</t>
+          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 137/2015. Ref. ao pagamento da NFS-e nº 13911, emitidas em 18/03/2015, com o devido atesto, disponibilidade de uso de recursos, Sist. Penitenci</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2020NE00069</t>
+          <t>2020NE00070</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19639.18</v>
+        <v>14124</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1587,19 +1587,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>REF AO 4º TA DO CT 01/2016-SEJUSC, CONTRATO DE PRESTAÇÃO DE SERVIÇOS TÉCNICOS DE INFORMÁTICA DE FORMA EVENTUAL PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES.</t>
+          <t>4º TA AO CT Nº 02/2016-SEJUSC, SERVIÇOS DE PROCESSAMENTO DE DADOS DO SISTEMA DE PROTOCOLO WEB (SPROWEB) PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020NE00070</t>
+          <t>2020NE00069</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14124</v>
+        <v>19639.18</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4º TA AO CT Nº 02/2016-SEJUSC, SERVIÇOS DE PROCESSAMENTO DE DADOS DO SISTEMA DE PROTOCOLO WEB (SPROWEB) PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES.</t>
+          <t>REF AO 4º TA DO CT 01/2016-SEJUSC, CONTRATO DE PRESTAÇÃO DE SERVIÇOS TÉCNICOS DE INFORMÁTICA DE FORMA EVENTUAL PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020NE00744</t>
+          <t>2020NE00742</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>52.35</v>
+        <v>14225.06</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anulação de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
+          <t>Anulação parcial de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020NE00743</t>
+          <t>2020NE00741</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>94337.73</v>
+        <v>6565.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anulação de saldo parcial em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
+          <t>Anulação de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020NE00742</t>
+          <t>2020NE00741</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14225.06</v>
+        <v>6565.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1721,14 +1721,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anulação parcial de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
+          <t>Anulação de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020NE00741</t>
+          <t>2020NE00742</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6565.6</v>
+        <v>14225.06</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1747,14 +1747,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anulação de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
+          <t>Anulação parcial de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020NE00741</t>
+          <t>2020NE00743</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6565.6</v>
+        <v>94337.73</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1773,14 +1773,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anulação de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
+          <t>Anulação de saldo parcial em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020NE00742</t>
+          <t>2020NE00744</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14225.06</v>
+        <v>52.35</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anulação parcial de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
+          <t>Anulação de saldo em atendimento ao DECRETO 43.042/2020 de encerramento do exercício 2020.</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2016NE00030</t>
+          <t>2016NE00028</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1918,7 +1918,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2016NE00028</t>
+          <t>2016NE00030</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1948,7 +1948,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2018NE00697</t>
+          <t>2018NE00690</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4716.51</v>
+        <v>7669.74</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1967,14 +1967,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO PARCIAL DE EMPENHO POR SALDO NO CONTRATO</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2018NE00688</t>
+          <t>2018NE00695</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1660.05</v>
+        <v>299.17</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1993,14 +1993,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>anulação de empenho por saldo de contrato</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2018NE00698</t>
+          <t>2018NE00689</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3316.17</v>
+        <v>11009.15</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2019,14 +2019,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO DE EMPENHO POR SALDO DE CONTRATO</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2018NE00696</t>
+          <t>2018NE00700</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4398.86</v>
+        <v>19801.86</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2018NE00700</t>
+          <t>2018NE00696</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>19801.86</v>
+        <v>4398.86</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2018NE00689</t>
+          <t>2018NE00698</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11009.15</v>
+        <v>3316.17</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2097,14 +2097,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO POR SALDO DE CONTRATO</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2018NE00695</t>
+          <t>2018NE00688</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>299.17</v>
+        <v>1660.05</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2123,14 +2123,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>anulação de empenho por saldo de contrato</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2018NE00690</t>
+          <t>2018NE00697</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7669.74</v>
+        <v>4716.51</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2149,21 +2149,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DE EMPENHO POR SALDO NO CONTRATO</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2015NE00458</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10/2011</t>
-        </is>
-      </c>
+          <t>2015NE00457</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>28/11/2015</t>
@@ -2179,17 +2175,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>5º TERMO ADITIVO AO CONTRATO 10/2011 PRORROGAÇÃO DE PRAZO VIGENCIA 28/11/2015 A 27/11/2016 VALOR GLOBAL R$ 4.393,32 VALOR MENSAL R$ 366,11</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO PARA AJUSTE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2015NE00457</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>2015NE00458</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10/2011</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>28/11/2015</t>
@@ -2205,19 +2205,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO PARA AJUSTE</t>
+          <t>5º TERMO ADITIVO AO CONTRATO 10/2011 PRORROGAÇÃO DE PRAZO VIGENCIA 28/11/2015 A 27/11/2016 VALOR GLOBAL R$ 4.393,32 VALOR MENSAL R$ 366,11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2022NE0000813</t>
+          <t>2022NE0000814</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3503.52</v>
+        <v>141516.13</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2235,19 +2235,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO N° 7/2021</t>
+          <t>2° TERMO ADITIVO AO CONTRATO Nº 007/2020 -SEJUSC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2022NE0000814</t>
+          <t>2022NE0000813</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>141516.13</v>
+        <v>3503.52</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2° TERMO ADITIVO AO CONTRATO Nº 007/2020 -SEJUSC</t>
+          <t>1º TERMO ADITIVO AO CONTRATO N° 7/2021</t>
         </is>
       </c>
     </row>
@@ -2392,14 +2392,10 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2023NE0000111</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>7/2021</t>
-        </is>
-      </c>
+          <t>2023NE0000110</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>28/02/2023</t>
@@ -2415,17 +2411,21 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Celebração do 2° Termo Aditivo ao Contrato n° 007/2021, com a PRODAM –PROCESSAMENTO DE DADOS AMAZONAS S.A que tem como objeto a prestação dos serviços de protocolo em plataforma Web (SPROWeb).</t>
+          <t>Cancelamento da NE 109 para ajustes.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2023NE0000110</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>2023NE0000111</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7/2021</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>28/02/2023</t>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cancelamento da NE 109 para ajustes.</t>
+          <t>Celebração do 2° Termo Aditivo ao Contrato n° 007/2021, com a PRODAM –PROCESSAMENTO DE DADOS AMAZONAS S.A que tem como objeto a prestação dos serviços de protocolo em plataforma Web (SPROWeb).</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2023NE00312</t>
+          <t>2023NE0000312</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2673,14 +2673,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hospedagem SAM</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2023NE0000312</t>
+          <t>2023NE00312</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2703,14 +2703,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Hospedagem SAM</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2015NE00349</t>
+          <t>2015NE00353</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>8039.22</v>
+        <v>12000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2729,14 +2729,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 118/2015. Serviços de acesso à rede internet/computador central, durante o mês de Outubro/14, conforme NFS-e 12075, de 13/10/2014, devidamen</t>
+          <t>descrição incorreta</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2015NE00352</t>
+          <t>2015NE00346</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12000</v>
+        <v>1162.78</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2755,14 +2755,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>descrição incorreta</t>
+          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 114/2015. Ref. ao pagamento das NFS-e nº 12439, emitidas em 12/11/2014, com o devido atesto, serviços de hospedagem e confecção de Website, mês</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2015NE00348</t>
+          <t>2015NE00355</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3471.35</v>
+        <v>12000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2781,14 +2781,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Folha de Informação de Despesas de Exercícios Anteriores nº 119/2015. Serviços de forma eventual, durante o mês de Dezembro/14, conforme NFS-e 12800, de 05/12/2014, devidamente atestada nos autos. CT </t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 117/2015. Serviços de disponibilidade de recursos do Sistema Penitenciário de Execuções Penais-SPEC, durante o mês de Outubro/14, conforme N</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2015NE00354</t>
+          <t>2015NE00357</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12000</v>
+        <v>1533.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2807,14 +2807,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Folha de Informação de Despesas de Exercícios Anteriores nº 116/2015. Serviços de disponibilidade de recursos do Sistema Penitenciário de Execuções Penais-SPEC, durante o mês de Setembro/14, conforme </t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 121/2015. Serviço especializado de informática de cessão do Sistema de Protocolo SPROWEB, durante o mês de Novembro/14, conforme NFS-e 12840</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2015NE00356</t>
+          <t>2015NE00347</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1611.5</v>
+        <v>1162.78</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2833,28 +2833,24 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 120/2015. Serviço especializado de informática de cessão do Sistema de Protocolo SPROWEB, durante o mês de Outubro/14, conforme NFS-e 12228,</t>
+          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 113/2015. Ref. ao pagamento das NFS-e nº 12076, emitidas em 13/10/2014, com o devido atesto, serviços de hospedagem e confecção de Website, mês</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2015NE00350</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>13/2012</t>
-        </is>
-      </c>
+          <t>2015NE00345</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>27/03/2015</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12000</v>
+        <v>1162.78</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2863,14 +2859,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Folha de Informação de Despesas de Exercícios Anteriores nº 116/2015. Serviços de disponibilidade de recursos do Sistema Penitenciário de Execuções Penais-SPEC, durante o mês de Setembro/14, conforme </t>
+          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 115/2015. Ref. ao pagamento das NFS-e nº 12801, emitidas em 05/12/2014, com o devido atesto, serviços de hospedagem e confecção de Website, mês</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2015NE00351</t>
+          <t>2015NE00358</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2880,7 +2876,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12000</v>
+        <v>1500</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2889,14 +2885,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 117/2015. Serviços de disponibilidade de recursos do Sistema Penitenciário de Execuções Penais-SPEC, durante o mês de Outubro/14, conforme N</t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 122/2015. Serviço especializado de informática de cessão do Sistema de Protocolo SPROWEB, durante o mês de Dezembro/14, conforme NFS-e 12967</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2015NE00358</t>
+          <t>2015NE00351</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2906,7 +2902,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1500</v>
+        <v>12000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2915,24 +2911,28 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 122/2015. Serviço especializado de informática de cessão do Sistema de Protocolo SPROWEB, durante o mês de Dezembro/14, conforme NFS-e 12967</t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 117/2015. Serviços de disponibilidade de recursos do Sistema Penitenciário de Execuções Penais-SPEC, durante o mês de Outubro/14, conforme N</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2015NE00345</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>2015NE00350</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>13/2012</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>27/03/2015</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1162.78</v>
+        <v>12000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2941,14 +2941,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 115/2015. Ref. ao pagamento das NFS-e nº 12801, emitidas em 05/12/2014, com o devido atesto, serviços de hospedagem e confecção de Website, mês</t>
+          <t xml:space="preserve">Folha de Informação de Despesas de Exercícios Anteriores nº 116/2015. Serviços de disponibilidade de recursos do Sistema Penitenciário de Execuções Penais-SPEC, durante o mês de Setembro/14, conforme </t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2015NE00347</t>
+          <t>2015NE00356</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1162.78</v>
+        <v>1611.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2967,14 +2967,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 113/2015. Ref. ao pagamento das NFS-e nº 12076, emitidas em 13/10/2014, com o devido atesto, serviços de hospedagem e confecção de Website, mês</t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 120/2015. Serviço especializado de informática de cessão do Sistema de Protocolo SPROWEB, durante o mês de Outubro/14, conforme NFS-e 12228,</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2015NE00357</t>
+          <t>2015NE00354</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1533.5</v>
+        <v>12000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2993,14 +2993,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 121/2015. Serviço especializado de informática de cessão do Sistema de Protocolo SPROWEB, durante o mês de Novembro/14, conforme NFS-e 12840</t>
+          <t xml:space="preserve">Folha de Informação de Despesas de Exercícios Anteriores nº 116/2015. Serviços de disponibilidade de recursos do Sistema Penitenciário de Execuções Penais-SPEC, durante o mês de Setembro/14, conforme </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2015NE00355</t>
+          <t>2015NE00348</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12000</v>
+        <v>3471.35</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3019,14 +3019,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 117/2015. Serviços de disponibilidade de recursos do Sistema Penitenciário de Execuções Penais-SPEC, durante o mês de Outubro/14, conforme N</t>
+          <t xml:space="preserve">Folha de Informação de Despesas de Exercícios Anteriores nº 119/2015. Serviços de forma eventual, durante o mês de Dezembro/14, conforme NFS-e 12800, de 05/12/2014, devidamente atestada nos autos. CT </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2015NE00346</t>
+          <t>2015NE00352</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1162.78</v>
+        <v>12000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3045,14 +3045,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Folha de Informação de Desp. de Exercícios Anteriores nº 114/2015. Ref. ao pagamento das NFS-e nº 12439, emitidas em 12/11/2014, com o devido atesto, serviços de hospedagem e confecção de Website, mês</t>
+          <t>descrição incorreta</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2015NE00353</t>
+          <t>2015NE00349</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12000</v>
+        <v>8039.22</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>descrição incorreta</t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº 118/2015. Serviços de acesso à rede internet/computador central, durante o mês de Outubro/14, conforme NFS-e 12075, de 13/10/2014, devidamen</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024NE0001326</t>
+          <t>2024NE0001327</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1735.93</v>
+        <v>333.83</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2024NE0001327</t>
+          <t>2024NE0001326</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>333.83</v>
+        <v>1735.93</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2019NE00291</t>
+          <t>2019NE00279</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1530.5</v>
+        <v>972.23</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2019NE00296</t>
+          <t>2019NE00280</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1550.81</v>
+        <v>812.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2019NE00301</t>
+          <t>2019NE00284</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1607.81</v>
+        <v>696.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2019NE00300</t>
+          <t>2019NE00283</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2745.09</v>
+        <v>4715.57</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2019NE00283</t>
+          <t>2019NE00300</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4715.57</v>
+        <v>2745.09</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2019NE00284</t>
+          <t>2019NE00301</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>696.2</v>
+        <v>1607.81</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2019NE00280</t>
+          <t>2019NE00296</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>812.1</v>
+        <v>1550.81</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2019NE00279</t>
+          <t>2019NE00291</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>972.23</v>
+        <v>1530.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3480,12 +3480,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2021NE0000114</t>
+          <t>2021NE0000113</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4616.08</v>
+        <v>9764.940000000001</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3503,19 +3503,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SITEMA DE PROTOCOLO WM PLATAFORMA WEB PAR ATENDER AS DEMANDAS DESTA SEJUSC PELO PERIODO DE 12 MESES</t>
+          <t>4° T.A CT 03/2017 - PRORROGAÇÃO DA VIGÊNCIA POR MAIS 12(DOZE) MESES, REFERENTE AOS SERVIÇOS DE SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM (SISTEMA DE ACOMPANHAMENT</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2021NE0000113</t>
+          <t>2021NE0000114</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>9764.940000000001</v>
+        <v>4616.08</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4° T.A CT 03/2017 - PRORROGAÇÃO DA VIGÊNCIA POR MAIS 12(DOZE) MESES, REFERENTE AOS SERVIÇOS DE SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM (SISTEMA DE ACOMPANHAMENT</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SITEMA DE PROTOCOLO WM PLATAFORMA WEB PAR ATENDER AS DEMANDAS DESTA SEJUSC PELO PERIODO DE 12 MESES</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2023NE0000937</t>
+          <t>2023NE0000938</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2069.76</v>
+        <v>7408.9</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3589,19 +3589,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2023NE0000938</t>
+          <t>2023NE0000937</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7408.9</v>
+        <v>2069.76</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3619,19 +3619,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2015NE00873</t>
+          <t>2015NE00869</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>42370.6</v>
+        <v>12440.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3656,12 +3656,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2015NE00880</t>
+          <t>2015NE00859</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>13/2012</t>
+          <t>2/2011</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>14623.1</v>
+        <v>3103.28</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3716,12 +3716,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2015NE00859</t>
+          <t>2015NE00880</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2/2011</t>
+          <t>13/2012</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3103.28</v>
+        <v>14623.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3746,12 +3746,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2015NE00869</t>
+          <t>2015NE00873</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12440.4</v>
+        <v>42370.6</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3802,12 +3802,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2017NE00578</t>
+          <t>2017NE00582</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1193.87</v>
+        <v>9079.719999999999</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3825,19 +3825,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM CESSÃO DE USO DE PROGRAMA, PLATAFORMA WEB SPROWEB</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM-SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2017NE00579</t>
+          <t>2017NE00576</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1660.05</v>
+        <v>73459.11</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL (SERVIÇOS EVENTUAIS)</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET (REDE MUNDIAL DE COMPUTADORES)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2017NE00576</t>
+          <t>2017NE00579</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>73459.11</v>
+        <v>1660.05</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3885,19 +3885,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNET (REDE MUNDIAL DE COMPUTADORES)</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL (SERVIÇOS EVENTUAIS)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2017NE00582</t>
+          <t>2017NE00578</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>9079.719999999999</v>
+        <v>1193.87</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM-SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM CESSÃO DE USO DE PROGRAMA, PLATAFORMA WEB SPROWEB</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2015NE00289</t>
+          <t>2015NE00283</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>39889.7</v>
+        <v>4738.13</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4061,14 +4061,14 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015.</t>
+          <t>SALDO DE CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2015NE00283</t>
+          <t>2015NE00289</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4738.13</v>
+        <v>39889.7</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SALDO DE CONTRATO.</t>
+          <t>Cobertura Financeira 2015.</t>
         </is>
       </c>
     </row>
@@ -4244,10 +4244,14 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2022NE0000390</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>2022NE0000395</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>8/2022</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
           <t>19/04/2022</t>
@@ -4263,21 +4267,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANULAÇÃO DA NOTA DE EMPENHO 2022NE0000369, REFERENTE A CONTRATAÇÃO DE SERVIÇOS DE HOSPEDAGEM DE SISTEMAS DE INFORMAÇÃO, CONTEMPLANDO O SISTEMA SAM-SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE </t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2022NE0000395</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>8/2022</t>
-        </is>
-      </c>
+          <t>2022NE0000390</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>19/04/2022</t>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t xml:space="preserve">ANULAÇÃO DA NOTA DE EMPENHO 2022NE0000369, REFERENTE A CONTRATAÇÃO DE SERVIÇOS DE HOSPEDAGEM DE SISTEMAS DE INFORMAÇÃO, CONTEMPLANDO O SISTEMA SAM-SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE </t>
         </is>
       </c>
     </row>
@@ -4326,14 +4326,10 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026NE0000001</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>8/2022</t>
-        </is>
-      </c>
+          <t>2026NE0000005</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>19/01/2026</t>
@@ -4349,17 +4345,21 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Contrataçao de Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informa</t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO Nº 01 PARA AJUSTES NA DATA INFORMADA.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026NE0000005</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>2026NE0000001</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>8/2022</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
           <t>19/01/2026</t>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO Nº 01 PARA AJUSTES NA DATA INFORMADA.</t>
+          <t>Contrataçao de Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informa</t>
         </is>
       </c>
     </row>
@@ -4438,17 +4438,21 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2017NE00386</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>2017NE00381</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>9/2013</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
           <t>18/12/2017</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>4773.32</v>
+        <v>677.28</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4457,24 +4461,28 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SALDO DE CONTRATO PARA AJUSTE ORÇAMENTÁRIO.</t>
+          <t>Contratação de empresa em prestação de serviços SPROWEB. 5º TA AO CT 09/2013</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2017NE00377</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>2017NE00382</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>7/2016</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr">
         <is>
           <t>18/12/2017</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>119.41</v>
+        <v>11093.36</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4483,14 +4491,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SALDO REMANESCENTE DE CONTRATO POR ESTIMATIVA</t>
+          <t xml:space="preserve">Contratação de empresa em prestação de serviços de link de comunicação, sistema de transmissão de dados, execução de sistema de informação, desenvolvimento de website e segurança da informação. 1º TA </t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2017NE00401</t>
+          <t>2017NE00400</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -4500,7 +4508,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>633.67</v>
+        <v>316.6</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4509,14 +4517,14 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Anulação saldo remanescente do Contrato nº 07/2016, em obediencia a Instrução Normativa nº 0001/2017 que dispoe sobre os procedimento para o encerramento do exercicio de 2017.</t>
+          <t>Anulação Saldo remanescente do Contrato nº 07/2016, em obediencia a Instrução Normativa nº 0001/2017-GSEFAZ, que dispoe sobre os procedimentos para o encerraemnto de exercício 2017.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2017NE00400</t>
+          <t>2017NE00401</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -4526,7 +4534,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>316.6</v>
+        <v>633.67</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4535,28 +4543,24 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Anulação Saldo remanescente do Contrato nº 07/2016, em obediencia a Instrução Normativa nº 0001/2017-GSEFAZ, que dispoe sobre os procedimentos para o encerraemnto de exercício 2017.</t>
+          <t>Anulação saldo remanescente do Contrato nº 07/2016, em obediencia a Instrução Normativa nº 0001/2017 que dispoe sobre os procedimento para o encerramento do exercicio de 2017.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2017NE00382</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>7/2016</t>
-        </is>
-      </c>
+          <t>2017NE00377</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
           <t>18/12/2017</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11093.36</v>
+        <v>119.41</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4565,28 +4569,24 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa em prestação de serviços de link de comunicação, sistema de transmissão de dados, execução de sistema de informação, desenvolvimento de website e segurança da informação. 1º TA </t>
+          <t>SALDO REMANESCENTE DE CONTRATO POR ESTIMATIVA</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2017NE00381</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>9/2013</t>
-        </is>
-      </c>
+          <t>2017NE00386</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
           <t>18/12/2017</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>677.28</v>
+        <v>4773.32</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Contratação de empresa em prestação de serviços SPROWEB. 5º TA AO CT 09/2013</t>
+          <t>SALDO DE CONTRATO PARA AJUSTE ORÇAMENTÁRIO.</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2017NE00316</t>
+          <t>2017NE00318</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, prestação de serviços eventuais nota fiscal nº 16712 de 26/11/2015 (abril/14), Termo Contrato nº 03/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, prestação de serviços eventuais nota fiscal nº 16714 de 26/11/2015 (junho/14), Termo Contrato nº 03/2011</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2017NE00317</t>
+          <t>2017NE00319</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, prestação de serviços eventuais nota fiscal nº 16713 de 26/11/2015 (maio/14), Termo Contrato nº 03/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, prestação de serviços eventuais nota fiscal nº 16715 de 26/11/2015 (julho/14), Termo Contrato nº 03/2011</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2017NE00319</t>
+          <t>2017NE00317</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, prestação de serviços eventuais nota fiscal nº 16715 de 26/11/2015 (julho/14), Termo Contrato nº 03/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, prestação de serviços eventuais nota fiscal nº 16713 de 26/11/2015 (maio/14), Termo Contrato nº 03/2011</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2017NE00318</t>
+          <t>2017NE00316</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4775,19 +4775,19 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, prestação de serviços eventuais nota fiscal nº 16714 de 26/11/2015 (junho/14), Termo Contrato nº 03/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, prestação de serviços eventuais nota fiscal nº 16712 de 26/11/2015 (abril/14), Termo Contrato nº 03/2011</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2023NE0000729</t>
+          <t>2023NE0000730</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2424.2</v>
+        <v>2403.59</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Celebração do 2° Termo Aditivo ao Contrato n° 007/2021, com a PRODAM –PROCESSAMENTO DE DADOS AMAZONAS S.A que tem como objeto a prestação dos serviços de protocolo em plataforma Web (SPROWeb). TC: 007</t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 019/2021 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2023NE0000730</t>
+          <t>2023NE0000729</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2403.59</v>
+        <v>2424.2</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 019/2021 AD: 01.</t>
+          <t>Celebração do 2° Termo Aditivo ao Contrato n° 007/2021, com a PRODAM –PROCESSAMENTO DE DADOS AMAZONAS S.A que tem como objeto a prestação dos serviços de protocolo em plataforma Web (SPROWeb). TC: 007</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2023NE0000007</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2335.68</v>
+        <v>283032.26</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5059,19 +5059,19 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Prorrogação da Vigência e Supressão do Valor Global do Contrato de Serviço de Sistema de Protocolo em Plataforma Web - SPROWEB, para atender as demandas desta SEJUSC.</t>
+          <t>Contratação de serviço de Rede de Governo incluindo o fornecimento de circuito de transmissão de dados entre o cliente e a Prodam, o Acesso Gerenciado a rede mundial Internet, sistemas contratados res</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2023NE0000008</t>
+          <t>2023NE0000006</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8279.040000000001</v>
+        <v>28618.76</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5089,19 +5089,19 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2023NE0000006</t>
+          <t>2023NE0000008</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>28618.76</v>
+        <v>8279.040000000001</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5119,19 +5119,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2023NE0000007</t>
+          <t>2023NE0000005</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>283032.26</v>
+        <v>2335.68</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5149,14 +5149,14 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Rede de Governo incluindo o fornecimento de circuito de transmissão de dados entre o cliente e a Prodam, o Acesso Gerenciado a rede mundial Internet, sistemas contratados res</t>
+          <t>Prorrogação da Vigência e Supressão do Valor Global do Contrato de Serviço de Sistema de Protocolo em Plataforma Web - SPROWEB, para atender as demandas desta SEJUSC.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2016NE00300</t>
+          <t>2016NE00304</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>328.35</v>
+        <v>11529.43</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5182,12 +5182,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2016NE00307</t>
+          <t>2016NE00303</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>10255.92</v>
+        <v>677.28</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5205,14 +5205,14 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ONTRATO Nº 07/2016 VIGÊNCIA 01/09/2016 A 31/08/2017 VALOR GLOBAL R$ 124.745,92 VALOR MENSAL R$ 10.255,92 EMPENHAR NO EXERCÍCIO SEGUINTE R$ 82.884,80 FUNDAMENTAÇÃO LEGAL: DISPENSA DE LICITAÇÃO RDL Nº 0</t>
+          <t xml:space="preserve">º TERMO ADITIVO AO CONTRATO Nº 09/2013, VIGÊNCIA: 27/09/2016 A 26/09/2017 VALOR GLOBAL: R$ 8.127,36 VALOR MENSAL: R$ 677,28 EMPENHAR NO EXERCÍCIO SEGUINTE R$ 6.095,52 FUNDAMENTAÇÃO LEGAL: DISPENSA DE </t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2016NE00299</t>
+          <t>2016NE00298</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -5238,7 +5238,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2016NE00298</t>
+          <t>2016NE00299</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5264,12 +5264,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2016NE00303</t>
+          <t>2016NE00307</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>677.28</v>
+        <v>10255.92</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5287,14 +5287,14 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">º TERMO ADITIVO AO CONTRATO Nº 09/2013, VIGÊNCIA: 27/09/2016 A 26/09/2017 VALOR GLOBAL: R$ 8.127,36 VALOR MENSAL: R$ 677,28 EMPENHAR NO EXERCÍCIO SEGUINTE R$ 6.095,52 FUNDAMENTAÇÃO LEGAL: DISPENSA DE </t>
+          <t>ONTRATO Nº 07/2016 VIGÊNCIA 01/09/2016 A 31/08/2017 VALOR GLOBAL R$ 124.745,92 VALOR MENSAL R$ 10.255,92 EMPENHAR NO EXERCÍCIO SEGUINTE R$ 82.884,80 FUNDAMENTAÇÃO LEGAL: DISPENSA DE LICITAÇÃO RDL Nº 0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2016NE00304</t>
+          <t>2016NE00300</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11529.43</v>
+        <v>328.35</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2015NE00484</t>
+          <t>2015NE00487</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>7191.21</v>
+        <v>22997.54</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2015NE00468</t>
+          <t>2015NE00485</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>148</v>
+        <v>1162.96</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5365,14 +5365,14 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL, PARA EMPENHAMENTO DA DESPESA DO CERTIFICADO DIGITAL</t>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2015NE00501</t>
+          <t>2015NE00489</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>366.11</v>
+        <v>2031.84</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2015NE00489</t>
+          <t>2015NE00501</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2031.84</v>
+        <v>366.11</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2015NE00485</t>
+          <t>2015NE00468</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1162.96</v>
+        <v>148</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5443,14 +5443,14 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO PARA AJUSTE ORÇAMENTÁRIO NO EXERCÍCIO DE 2015</t>
+          <t>ANULAÇÃO PARCIAL, PARA EMPENHAMENTO DA DESPESA DO CERTIFICADO DIGITAL</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2015NE00487</t>
+          <t>2015NE00484</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>22997.54</v>
+        <v>7191.21</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5502,12 +5502,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2023NE0000366</t>
+          <t>2023NE0000367</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4139.52</v>
+        <v>2424.2</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5525,19 +5525,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 019/2021 AD: 01.</t>
+          <t>Celebração do 2° Termo Aditivo ao Contrato n° 007/2021, com a PRODAM –PROCESSAMENTO DE DADOS AMAZONAS S.A que tem como objeto a prestação dos serviços de protocolo em plataforma Web (SPROWeb). TC: 007</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2023NE0000367</t>
+          <t>2023NE0000366</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>2424.2</v>
+        <v>4139.52</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5555,19 +5555,19 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Celebração do 2° Termo Aditivo ao Contrato n° 007/2021, com a PRODAM –PROCESSAMENTO DE DADOS AMAZONAS S.A que tem como objeto a prestação dos serviços de protocolo em plataforma Web (SPROWeb). TC: 007</t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 019/2021 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2018NE00080</t>
+          <t>2018NE00081</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>63525.12</v>
+        <v>4740.96</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5585,14 +5585,14 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Contratação de empresa em prestação de serviços de link de comunicação, sistema de transmissão de dados, execução de sistema de informação, desenvolvimento de website e segurança da informação.</t>
+          <t>Contratação de prestação de serviços SPROWEB CT 09/2013</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2018NE00071</t>
+          <t>2018NE00072</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>63525.12</v>
+        <v>4740.96</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2018NE00072</t>
+          <t>2018NE00071</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4740.96</v>
+        <v>63525.12</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5644,12 +5644,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2018NE00081</t>
+          <t>2018NE00080</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4740.96</v>
+        <v>63525.12</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5667,14 +5667,14 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviços SPROWEB CT 09/2013</t>
+          <t>Contratação de empresa em prestação de serviços de link de comunicação, sistema de transmissão de dados, execução de sistema de informação, desenvolvimento de website e segurança da informação.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2015NE00327</t>
+          <t>2015NE00328</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>817.9</v>
+        <v>21891.32</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5693,14 +5693,14 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE EXERCÍCIO ANTERIORES Nº 003/2015 PRESTAÇÃO DE SERVIÇOS DE DESENVOLVIMENTO DE CONFECÇÃO E IMPLANTAÇÃO DE WEB SITE DOS MESES DE OUTUBRO E NOVEMBRO DE 201</t>
+          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE EXERCÍCIO ANTERIORES Nº 004/2015 PRESTAÇÃO DE SERVIÇOS ACESSO A INTERNET E FOLHA DE PAGAMENTO. FUNDAMENTAÇÃO LEGAL: PROCESSO Nº 636/2014 REFERENTE AO M</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2015NE00328</t>
+          <t>2015NE00327</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -5710,7 +5710,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>21891.32</v>
+        <v>817.9</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE EXERCÍCIO ANTERIORES Nº 004/2015 PRESTAÇÃO DE SERVIÇOS ACESSO A INTERNET E FOLHA DE PAGAMENTO. FUNDAMENTAÇÃO LEGAL: PROCESSO Nº 636/2014 REFERENTE AO M</t>
+          <t>RECONHECIMENTO DA DIVIDA: FOLHA DE INFORMAÇÃO DE EXERCÍCIO ANTERIORES Nº 003/2015 PRESTAÇÃO DE SERVIÇOS DE DESENVOLVIMENTO DE CONFECÇÃO E IMPLANTAÇÃO DE WEB SITE DOS MESES DE OUTUBRO E NOVEMBRO DE 201</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2019NE00631</t>
+          <t>2019NE00633</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>78417.46000000001</v>
+        <v>4882.47</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5779,19 +5779,19 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>REF, A PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES. CT 12/2016-SEJUSC, MÊS:DEZEMBRO/2019</t>
+          <t>REF A PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DE SISTEMA-SAM CT 03/2017-SEJUSC, MÊS:DEZEMBRO/2019</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2019NE00629</t>
+          <t>2019NE00630</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1284</v>
+        <v>1785.38</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5809,19 +5809,19 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>REF A PRESTAÇÃO DE SERVIÇOS DE SISTEMA SPROWEB - CT 02/2016-SEJUSC MÊS: DEZEMBRO</t>
+          <t>REF A PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES CT 01/2016-SEJUSC MÊS:DEZEMBRO/2019</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2019NE00630</t>
+          <t>2019NE00629</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1785.38</v>
+        <v>1284</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5839,19 +5839,19 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>REF A PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES CT 01/2016-SEJUSC MÊS:DEZEMBRO/2019</t>
+          <t>REF A PRESTAÇÃO DE SERVIÇOS DE SISTEMA SPROWEB - CT 02/2016-SEJUSC MÊS: DEZEMBRO</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2019NE00633</t>
+          <t>2019NE00631</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4882.47</v>
+        <v>78417.46000000001</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>REF A PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DE SISTEMA-SAM CT 03/2017-SEJUSC, MÊS:DEZEMBRO/2019</t>
+          <t>REF, A PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES. CT 12/2016-SEJUSC, MÊS:DEZEMBRO/2019</t>
         </is>
       </c>
     </row>
@@ -6138,12 +6138,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021NE0000242</t>
+          <t>2021NE0000243</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>9232.16</v>
+        <v>19529.88</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6161,19 +6161,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>REFERENTE AO REFOR DA NE=00114/2021- CONTRATO N° 07/2021- CONTRATAÇÃO DE PESSOA JURIDICA NA PRESTAÇÃO DE SERVIÇOS DE DE EXECUÇÃO DE SISTEMA PROTOCOLO EM PLATAFORMA SPROWEB PARA ATENDER AS DEMANDAS DES</t>
+          <t>REFORÇO DA NE=00113/2021- REF. 4º TERMO ADITIV AO CNTRATO Nº SERVIÇOS DE SISTEMA DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM.(SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇ</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2021NE0000243</t>
+          <t>2021NE0000242</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>19529.88</v>
+        <v>9232.16</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE=00113/2021- REF. 4º TERMO ADITIV AO CNTRATO Nº SERVIÇOS DE SISTEMA DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM.(SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇ</t>
+          <t>REFERENTE AO REFOR DA NE=00114/2021- CONTRATO N° 07/2021- CONTRATAÇÃO DE PESSOA JURIDICA NA PRESTAÇÃO DE SERVIÇOS DE DE EXECUÇÃO DE SISTEMA PROTOCOLO EM PLATAFORMA SPROWEB PARA ATENDER AS DEMANDAS DES</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2024NE0000945</t>
+          <t>2024NE0000944</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>4139.52</v>
+        <v>14817.8</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6277,19 +6277,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 03.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2024NE0000944</t>
+          <t>2024NE0000945</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>14817.8</v>
+        <v>4139.52</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2017NE00158</t>
+          <t>2017NE00157</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2709.12</v>
+        <v>41861.12</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6397,19 +6397,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviços de licença de uso de sistema de informação, Sistema de Protocolo em Plataforma web (SPROWEB).</t>
+          <t>Contratação de prestação de serviço de acesso à rede de internet e computador central, serviço de processamento do sistema CFPP e serviços eventuais de informatica.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2017NE00157</t>
+          <t>2017NE00158</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6418,7 +6418,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>41861.12</v>
+        <v>2709.12</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de acesso à rede de internet e computador central, serviço de processamento do sistema CFPP e serviços eventuais de informatica.</t>
+          <t>Contratação de prestação de serviços de licença de uso de sistema de informação, Sistema de Protocolo em Plataforma web (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -6606,12 +6606,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2022NE0000134</t>
+          <t>2022NE0000132</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1895.19</v>
+        <v>260580.84</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6629,19 +6629,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CT 19/21</t>
+          <t>CT 07/20</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2022NE0000132</t>
+          <t>2022NE0000134</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>260580.84</v>
+        <v>1895.19</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6659,19 +6659,19 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CT 07/20</t>
+          <t>CT 19/21</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2023NE0000981</t>
+          <t>2023NE0000980</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>7408.9</v>
+        <v>2069.76</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6689,19 +6689,19 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2023NE0000980</t>
+          <t>2023NE0000981</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2069.76</v>
+        <v>7408.9</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
@@ -6756,12 +6756,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2019NE00488</t>
+          <t>2019NE00487</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>156834.92</v>
+        <v>3570.76</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6779,19 +6779,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>46139 - SERVIÇOS DE ACESSO À INTERNET, Descrição: SERVIÇOS DE ACESSO À INTERNET, Descrição: contratação de empresa especializada na prestação de serviço de acesso à rede mundial de computadores (Inter</t>
+          <t xml:space="preserve">59261 - SERVIÇOS DE INFORMÁTICA, Descrição: SERVIÇOS DE INFORMÁTICA, Descrição: Contratação de empresa para prestação de serviços de informática em geral, conforme projeto básico MARCA: null 3º TERMO </t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2019NE00486</t>
+          <t>2019NE00489</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2568</v>
+        <v>9764.940000000001</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6809,19 +6809,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">79330 - SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA </t>
+          <t>117367 - HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, : HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para prestação de serviço de hospedagem do Sistema de Acompanhament</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2019NE00489</t>
+          <t>2019NE00486</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>9764.940000000001</v>
+        <v>2568</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6839,19 +6839,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>117367 - HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, : HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para prestação de serviço de hospedagem do Sistema de Acompanhament</t>
+          <t xml:space="preserve">79330 - SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA </t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2019NE00487</t>
+          <t>2019NE00488</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>3570.76</v>
+        <v>156834.92</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">59261 - SERVIÇOS DE INFORMÁTICA, Descrição: SERVIÇOS DE INFORMÁTICA, Descrição: Contratação de empresa para prestação de serviços de informática em geral, conforme projeto básico MARCA: null 3º TERMO </t>
+          <t>46139 - SERVIÇOS DE ACESSO À INTERNET, Descrição: SERVIÇOS DE ACESSO À INTERNET, Descrição: contratação de empresa especializada na prestação de serviço de acesso à rede mundial de computadores (Inter</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2024NE0000140</t>
+          <t>2024NE0000139</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>4139.52</v>
+        <v>14817.8</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7019,19 +7019,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2024NE0000139</t>
+          <t>2024NE0000140</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>14817.8</v>
+        <v>4139.52</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7049,19 +7049,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2018NE00593</t>
+          <t>2018NE00594</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>220377.33</v>
+        <v>4425.87</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7079,19 +7079,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>REF. 2º TA AO CONTRATO Nº 12/2016-SEJUSC, REF AMPLIAÇÃO DA PRESTAÇÃO DE SERVIÇOS DE REDE DE INTERNET. MESES: SETEMBRO/2018 A NOVEMBRO/2018</t>
+          <t>2º TA AO CONTRATO Nº 034/2016-SEJUSC, PREST DE SERVIÇOS NO DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL DA SEJUSC. MESES: SETEMBRO/2018 A NOVEMBRO/2018</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2018NE00596</t>
+          <t>2018NE00595</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>13619.58</v>
+        <v>4980.15</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7109,19 +7109,19 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>1º TA AO CONTRATO Nº 003/2017-SEJUSC, PREST DE SERVIÇOS DE HOSPEDAGEM DE INFORMAÇÃO (SAM), MESES: SETEMBRO/2018 A NOVEMBRO/2018</t>
+          <t>2º TA AO CONTRATO Nº 001/2016-SEJUSC, PREST DE SERVIÇOS DE INFORMÁTICA EM GERAL. MESES: SETEMBRO/2018 A NOVEMBRO/2018</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2018NE00595</t>
+          <t>2018NE00596</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>4980.15</v>
+        <v>13619.58</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7139,19 +7139,19 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2º TA AO CONTRATO Nº 001/2016-SEJUSC, PREST DE SERVIÇOS DE INFORMÁTICA EM GERAL. MESES: SETEMBRO/2018 A NOVEMBRO/2018</t>
+          <t>1º TA AO CONTRATO Nº 003/2017-SEJUSC, PREST DE SERVIÇOS DE HOSPEDAGEM DE INFORMAÇÃO (SAM), MESES: SETEMBRO/2018 A NOVEMBRO/2018</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2018NE00594</t>
+          <t>2018NE00593</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>4425.87</v>
+        <v>220377.33</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2º TA AO CONTRATO Nº 034/2016-SEJUSC, PREST DE SERVIÇOS NO DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL DA SEJUSC. MESES: SETEMBRO/2018 A NOVEMBRO/2018</t>
+          <t>REF. 2º TA AO CONTRATO Nº 12/2016-SEJUSC, REF AMPLIAÇÃO DA PRESTAÇÃO DE SERVIÇOS DE REDE DE INTERNET. MESES: SETEMBRO/2018 A NOVEMBRO/2018</t>
         </is>
       </c>
     </row>
@@ -7326,17 +7326,21 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2019NE00694</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
+          <t>2019NE00698</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>12/2016</t>
+        </is>
+      </c>
       <c r="C237" t="inlineStr">
         <is>
           <t>05/12/2019</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>78417.46000000001</v>
+        <v>72091.16</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7345,28 +7349,24 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE PARA AJUSTE ORÇAMENTÁRIO.</t>
+          <t>REF AO 4º TA AO CT Nº 12/2016-SEJUSC SERVIÇOS DE ACESSO A INTERNET.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2019NE00698</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>12/2016</t>
-        </is>
-      </c>
+          <t>2019NE00694</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
           <t>05/12/2019</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>72091.16</v>
+        <v>78417.46000000001</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7375,14 +7375,14 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>REF AO 4º TA AO CT Nº 12/2016-SEJUSC SERVIÇOS DE ACESSO A INTERNET.</t>
+          <t>ANULAÇÃO DA NE PARA AJUSTE ORÇAMENTÁRIO.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021NE0000776</t>
+          <t>2021NE0000777</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>818.66</v>
+        <v>826.26</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7401,14 +7401,14 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Serviço é referente ao processamento de Folha especial TIPO 65 no mês de maio/2021.</t>
+          <t>Reconhecimento de dívida que trata do ressarcimento de valores relativos à prestação de serviço referente ao processamento de Folha especial TIPO 6 3 no mês de maio/2021.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021NE0000777</t>
+          <t>2021NE0000776</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>826.26</v>
+        <v>818.66</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Reconhecimento de dívida que trata do ressarcimento de valores relativos à prestação de serviço referente ao processamento de Folha especial TIPO 6 3 no mês de maio/2021.</t>
+          <t>Serviço é referente ao processamento de Folha especial TIPO 65 no mês de maio/2021.</t>
         </is>
       </c>
     </row>
@@ -7494,12 +7494,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026NE0000006</t>
+          <t>2026NE0000002</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>30967.04</v>
+        <v>8735.719999999999</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7517,19 +7517,19 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Contrataçao de Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informa</t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026NE0000002</t>
+          <t>2026NE0000006</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>8735.719999999999</v>
+        <v>30967.04</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7547,19 +7547,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 04.</t>
+          <t>Contrataçao de Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informa</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2015NE00096</t>
+          <t>2015NE00082</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>13/2012</t>
+          <t>7/2010</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>43869.3</v>
+        <v>25622.64</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7577,19 +7577,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>data de vigência no detacontrato incorreta</t>
+          <t>OBJETO: SALDO DO 6º TA AO CONTRATO Nº 007/2010 PARA O EXERCÍCIO DE 2015. VIGÊNCIA: 02/11/2014 a 02/11/2015 VALOR GLOBAL: R$ 102.490,56 VALOR MENSAL: R$ 8.540,88 FUNDAMENTO LEGAL:Mem nº 399/2014/GCC/DE</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2015NE00089</t>
+          <t>2015NE00036</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>13/2012</t>
+          <t>2/2011</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>43869.3</v>
+        <v>7925.25</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7607,14 +7607,14 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>OBJETO: SALDO DO 2º TA AO CONTRATO Nº 013/2012 PARA O EXERCÍCIO DE 2015, Contemplando Reajuste de acordo com IGPM. VIGÊNCIA: 02/11/2014 a 02/11/2015 VALOR GLOBAL: R$ 175.477,20 VALOR MENSAL: R$ 14.623</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2015NE00083</t>
+          <t>2015NE00084</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>DESCRIÇÃO INCOMPLETA</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2015NE00084</t>
+          <t>2015NE00083</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7697,19 +7697,19 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>DESCRIÇÃO INCOMPLETA</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2015NE00036</t>
+          <t>2015NE00089</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2/2011</t>
+          <t>13/2012</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>7925.25</v>
+        <v>43869.3</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7727,19 +7727,19 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>OBJETO: SALDO DO 2º TA AO CONTRATO Nº 013/2012 PARA O EXERCÍCIO DE 2015, Contemplando Reajuste de acordo com IGPM. VIGÊNCIA: 02/11/2014 a 02/11/2015 VALOR GLOBAL: R$ 175.477,20 VALOR MENSAL: R$ 14.623</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2015NE00016</t>
+          <t>2015NE00096</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>13/2012</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>2390.4</v>
+        <v>43869.3</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7757,19 +7757,19 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>data de vigência no detacontrato incorreta</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2015NE00015</t>
+          <t>2015NE00017</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>3/2011</t>
+          <t>10/2011</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>36963.23</v>
+        <v>1292.16</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7787,19 +7787,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>Empenho de contrato: importado manualmente em 21/09/2015</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2015NE00017</t>
+          <t>2015NE00015</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>10/2011</t>
+          <t>3/2011</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1292.16</v>
+        <v>36963.23</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7817,19 +7817,19 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Empenho de contrato: importado manualmente em 21/09/2015</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2015NE00082</t>
+          <t>2015NE00016</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7/2010</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>25622.64</v>
+        <v>2390.4</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>OBJETO: SALDO DO 6º TA AO CONTRATO Nº 007/2010 PARA O EXERCÍCIO DE 2015. VIGÊNCIA: 02/11/2014 a 02/11/2015 VALOR GLOBAL: R$ 102.490,56 VALOR MENSAL: R$ 8.540,88 FUNDAMENTO LEGAL:Mem nº 399/2014/GCC/DE</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2023NE0000793</t>
+          <t>2023NE0000791</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7894,7 +7894,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>2069.76</v>
+        <v>7408.9</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -7903,19 +7903,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2023NE0000791</t>
+          <t>2023NE0000793</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>7408.9</v>
+        <v>2069.76</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -8000,17 +8000,21 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2018NE00363</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr"/>
+          <t>2018NE00364</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>34/2016</t>
+        </is>
+      </c>
       <c r="C260" t="inlineStr">
         <is>
           <t>04/06/2018</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>146918.22</v>
+        <v>2950.58</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8019,14 +8023,14 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2º TA AO CT 12/2016 - PRESTAÇÃO DE SERVIÇOS DE REDE INTERNET DE 20MBPS PARA 57,20MBPS MESES: JULHO E AGOSTO/2018</t>
+          <t>1º TA AO CT 34/2016 - DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL SEJUSC MESES: JULHO E AGOSTO/2018</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2018NE00366</t>
+          <t>2018NE00361</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -8036,7 +8040,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>146918.22</v>
+        <v>2387.74</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8045,14 +8049,14 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>PARA AJUSTES</t>
+          <t>2º TA AO CT 002/2016 - PLATAFORMA SPROWEB MÊS: JULHO E AGOSTO/2018</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2018NE00393</t>
+          <t>2018NE00378</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -8062,7 +8066,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>146918.22</v>
+        <v>1475.29</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8071,24 +8075,28 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2º TA. AO CONTRATO 12/2016-SERV.PREST.INTERNET SEJUSC E DEMAIS UNIDADES-VIGÊNCIA: 07/04/2018-07/04/2019. MESES: JULHO E AGOSTO/2018</t>
+          <t>ANULAÇÃO CONFORME VIGENCIA</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2018NE00362</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr"/>
+          <t>2018NE00365</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C263" t="inlineStr">
         <is>
           <t>04/06/2018</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3320.1</v>
+        <v>9079.719999999999</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8097,28 +8105,24 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2º TA AO CT 001/2016 - SERVIÇOS EVENTUAIS DE INFORMÁTICA MESES: JULHO E AGOSTO/2018</t>
+          <t>1º TA AO CT 3/2017 - SISTEMA DE INFORMAÇÃO SAM MESES: JULHO E AGOSTO/2018</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2018NE00365</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2018NE00362</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
         <is>
           <t>04/06/2018</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>9079.719999999999</v>
+        <v>3320.1</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8127,14 +8131,14 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>1º TA AO CT 3/2017 - SISTEMA DE INFORMAÇÃO SAM MESES: JULHO E AGOSTO/2018</t>
+          <t>2º TA AO CT 001/2016 - SERVIÇOS EVENTUAIS DE INFORMÁTICA MESES: JULHO E AGOSTO/2018</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2018NE00378</t>
+          <t>2018NE00393</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -8144,7 +8148,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1475.29</v>
+        <v>146918.22</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8153,14 +8157,14 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>ANULAÇÃO CONFORME VIGENCIA</t>
+          <t>2º TA. AO CONTRATO 12/2016-SERV.PREST.INTERNET SEJUSC E DEMAIS UNIDADES-VIGÊNCIA: 07/04/2018-07/04/2019. MESES: JULHO E AGOSTO/2018</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2018NE00361</t>
+          <t>2018NE00366</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -8170,7 +8174,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>2387.74</v>
+        <v>146918.22</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8179,28 +8183,24 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2º TA AO CT 002/2016 - PLATAFORMA SPROWEB MÊS: JULHO E AGOSTO/2018</t>
+          <t>PARA AJUSTES</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2018NE00364</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>34/2016</t>
-        </is>
-      </c>
+          <t>2018NE00363</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr">
         <is>
           <t>04/06/2018</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2950.58</v>
+        <v>146918.22</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8209,19 +8209,19 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>1º TA AO CT 34/2016 - DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL SEJUSC MESES: JULHO E AGOSTO/2018</t>
+          <t>2º TA AO CT 12/2016 - PRESTAÇÃO DE SERVIÇOS DE REDE INTERNET DE 20MBPS PARA 57,20MBPS MESES: JULHO E AGOSTO/2018</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2021NE0000009</t>
+          <t>2021NE0000012</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1284</v>
+        <v>1785.38</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8239,19 +8239,19 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO (SPROWEB), PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES.</t>
+          <t>PRORROGAÇÃO DE PRAZO DE VIGÊNCIA DO CONTRATO DE PRESTAÇÃO DE SERVIÇOS EVENTUAIS, POR MAIS 12 (DOZE) MESES.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2021NE0000015</t>
+          <t>2021NE0000016</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>9764.940000000001</v>
+        <v>10422.21</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8269,19 +8269,19 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM (SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR).</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM GERENCIAMENTO DE CONTEÚDO PARA ATENDER AS DEMANDAS DA SEJUSC DE JANEIRO À JULHO E AGOSTO PARCIAL.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2021NE0000016</t>
+          <t>2021NE0000015</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>10422.21</v>
+        <v>9764.940000000001</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8299,19 +8299,19 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM GERENCIAMENTO DE CONTEÚDO PARA ATENDER AS DEMANDAS DA SEJUSC DE JANEIRO À JULHO E AGOSTO PARCIAL.</t>
+          <t>SERVIÇOS DE SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM (SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR).</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2021NE0000012</t>
+          <t>2021NE0000009</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1785.38</v>
+        <v>1284</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8329,19 +8329,19 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DE PRAZO DE VIGÊNCIA DO CONTRATO DE PRESTAÇÃO DE SERVIÇOS EVENTUAIS, POR MAIS 12 (DOZE) MESES.</t>
+          <t>SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO (SPROWEB), PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2016NE00018</t>
+          <t>2016NE00046</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>4063.68</v>
+        <v>11945.91</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8359,19 +8359,19 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISPENSA DE LICITAÇÃO RDL Nº 04/2013 PORTARIA DE DISPENSA DE LICITAÇÃO Nº 69 PUBLICADA NO D.O.E 11/12/2012 Contratação da prestação de serviços de uso de programas de computação para disponibilização </t>
+          <t>REF. SERVICO DE CONEXÃO DE INTERNET BANDA LARGA</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2016NE00012</t>
+          <t>2016NE00011</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>10/2011</t>
+          <t>3/2011</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>2196.66</v>
+        <v>59834.58</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8389,19 +8389,19 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FUNDAMENTAÇÃO LEGAL: DISPENSA DE LICITAÇÃO RDL Nº 4/2011, PORTARIA DE DISPENSA Nº 09/2011 GSEPED, PUBLICADO NO D.O.E 07/11/2011 SALDO DO 5º TERMO ADITIVO AO CONTRATO Nº 10/2011 FIRMADO COM ESTA SECRET</t>
+          <t>FUNDAMENTAÇÃO LEGAL: DISPENSA DE LICITAÇÃO RDL Nº 001/2011, PUBLICADO NO D.O.E 07/11/2011 SALDO DO 5º TERMO ADITIVO AO CONTRATO Nº 03/2011 FIRMADO COM ESTA SECRETARIA, VIGÊNCIA 22/08/2015 A 21/08/2016</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2016NE00011</t>
+          <t>2016NE00012</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>3/2011</t>
+          <t>10/2011</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>59834.58</v>
+        <v>2196.66</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8419,19 +8419,19 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>FUNDAMENTAÇÃO LEGAL: DISPENSA DE LICITAÇÃO RDL Nº 001/2011, PUBLICADO NO D.O.E 07/11/2011 SALDO DO 5º TERMO ADITIVO AO CONTRATO Nº 03/2011 FIRMADO COM ESTA SECRETARIA, VIGÊNCIA 22/08/2015 A 21/08/2016</t>
+          <t>FUNDAMENTAÇÃO LEGAL: DISPENSA DE LICITAÇÃO RDL Nº 4/2011, PORTARIA DE DISPENSA Nº 09/2011 GSEPED, PUBLICADO NO D.O.E 07/11/2011 SALDO DO 5º TERMO ADITIVO AO CONTRATO Nº 10/2011 FIRMADO COM ESTA SECRET</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2016NE00046</t>
+          <t>2016NE00018</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>11945.91</v>
+        <v>4063.68</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8449,24 +8449,28 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>REF. SERVICO DE CONEXÃO DE INTERNET BANDA LARGA</t>
+          <t xml:space="preserve">DISPENSA DE LICITAÇÃO RDL Nº 04/2013 PORTARIA DE DISPENSA DE LICITAÇÃO Nº 69 PUBLICADA NO D.O.E 11/12/2012 Contratação da prestação de serviços de uso de programas de computação para disponibilização </t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2016NE00667</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
+          <t>2016NE00652</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>12/2016</t>
+        </is>
+      </c>
       <c r="C276" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1097.41</v>
+        <v>68872.13</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8475,7 +8479,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>79330 ¿ (ID-79330) SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPRO</t>
+          <t xml:space="preserve">46139 ¿ (ID-46139) SERVIÇOS DE ACESSO À INTERNET, Descrição: contratação de empresa especializada na prestação de serviço de acesso à rede mundial de computadores (Internet), conforme discriminado em </t>
         </is>
       </c>
     </row>
@@ -8485,11 +8489,7 @@
           <t>2016NE00668</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>1/2016</t>
-        </is>
-      </c>
+      <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
           <t>03/10/2016</t>
@@ -8512,21 +8512,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2016NE00653</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>7/2016</t>
-        </is>
-      </c>
+          <t>2016NE00665</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>543.0599999999999</v>
+        <v>1475.29</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -8535,28 +8531,24 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>113680 ¿ (ID 113680) SERVIÇOS DE INFORMÁTICA, Descrição: contratação de empresa especializada na prestação de serviço de hospedagem para Website, conforme Projeto Básico. MARCA: Web Site Termo de Cont</t>
+          <t>93841 ¿ (ID-93841) DESENVOLVIMENTO DE WEB SITE, Descrição: Contratação de empresa especializada em desenvolvimento de Website Institucional com sistema de gerenciamento de conteúdo. INFORMAÇÕES ADICIO</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2016NE00653</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>7/2016</t>
-        </is>
-      </c>
+          <t>2016NE00665</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>543.0599999999999</v>
+        <v>1475.29</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8565,28 +8557,24 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>113680 ¿ (ID 113680) SERVIÇOS DE INFORMÁTICA, Descrição: contratação de empresa especializada na prestação de serviço de hospedagem para Website, conforme Projeto Básico. MARCA: Web Site Termo de Cont</t>
+          <t>93841 ¿ (ID-93841) DESENVOLVIMENTO DE WEB SITE, Descrição: Contratação de empresa especializada em desenvolvimento de Website Institucional com sistema de gerenciamento de conteúdo. INFORMAÇÕES ADICIO</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2016NE00667</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2016NE00652</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1097.41</v>
+        <v>68872.13</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8595,24 +8583,28 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>79330 ¿ (ID-79330) SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPRO</t>
+          <t xml:space="preserve">46139 ¿ (ID-46139) SERVIÇOS DE ACESSO À INTERNET, Descrição: contratação de empresa especializada na prestação de serviço de acesso à rede mundial de computadores (Internet), conforme discriminado em </t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2016NE00652</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr"/>
+          <t>2016NE00667</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C281" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>68872.13</v>
+        <v>1097.41</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -8621,24 +8613,28 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">46139 ¿ (ID-46139) SERVIÇOS DE ACESSO À INTERNET, Descrição: contratação de empresa especializada na prestação de serviço de acesso à rede mundial de computadores (Internet), conforme discriminado em </t>
+          <t>79330 ¿ (ID-79330) SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPRO</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2016NE00665</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr"/>
+          <t>2016NE00653</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>7/2016</t>
+        </is>
+      </c>
       <c r="C282" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1475.29</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8647,24 +8643,28 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>93841 ¿ (ID-93841) DESENVOLVIMENTO DE WEB SITE, Descrição: Contratação de empresa especializada em desenvolvimento de Website Institucional com sistema de gerenciamento de conteúdo. INFORMAÇÕES ADICIO</t>
+          <t>113680 ¿ (ID 113680) SERVIÇOS DE INFORMÁTICA, Descrição: contratação de empresa especializada na prestação de serviço de hospedagem para Website, conforme Projeto Básico. MARCA: Web Site Termo de Cont</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2016NE00665</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr"/>
+          <t>2016NE00653</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>7/2016</t>
+        </is>
+      </c>
       <c r="C283" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1475.29</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>93841 ¿ (ID-93841) DESENVOLVIMENTO DE WEB SITE, Descrição: Contratação de empresa especializada em desenvolvimento de Website Institucional com sistema de gerenciamento de conteúdo. INFORMAÇÕES ADICIO</t>
+          <t>113680 ¿ (ID 113680) SERVIÇOS DE INFORMÁTICA, Descrição: contratação de empresa especializada na prestação de serviço de hospedagem para Website, conforme Projeto Básico. MARCA: Web Site Termo de Cont</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,11 @@
           <t>2016NE00668</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1/2016</t>
+        </is>
+      </c>
       <c r="C284" t="inlineStr">
         <is>
           <t>03/10/2016</t>
@@ -8706,21 +8710,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2016NE00652</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>12/2016</t>
-        </is>
-      </c>
+          <t>2016NE00667</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>68872.13</v>
+        <v>1097.41</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">46139 ¿ (ID-46139) SERVIÇOS DE ACESSO À INTERNET, Descrição: contratação de empresa especializada na prestação de serviço de acesso à rede mundial de computadores (Internet), conforme discriminado em </t>
+          <t>79330 ¿ (ID-79330) SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPRO</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2023NE0000707</t>
+          <t>2023NE00707</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8759,14 +8759,14 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
+          <t>2º Termo Aditivo ao Contrato 019/2021.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2023NE00707</t>
+          <t>2023NE0000707</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Contrato 019/2021.</t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -8886,12 +8886,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2024NE0000377</t>
+          <t>2024NE0000378</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>7408.9</v>
+        <v>4139.52</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -8909,19 +8909,19 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2024NE0000378</t>
+          <t>2024NE0000377</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>4139.52</v>
+        <v>7408.9</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -8939,17 +8939,21 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2015NE00240</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr"/>
+          <t>2015NE00223</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>13/2012</t>
+        </is>
+      </c>
       <c r="C293" t="inlineStr">
         <is>
           <t>03/03/2015</t>
@@ -8965,14 +8969,14 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>vigência incorreta</t>
+          <t>OBJETO: SALDO DO 2º TA AO CONTRATO Nº 013/2012 PARA O EXERCÍCIO DE 2015, Contemplando Reajuste de acordo com IGPM. VIGÊNCIA: 02/11/2014 a 02/11/2015 VALOR GLOBAL: R$ 175.477,20 VALOR MENSAL: R$ 14.623</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2015NE00241</t>
+          <t>2015NE00224</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8995,7 +8999,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>descrição incompleta</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9036,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2015NE00224</t>
+          <t>2015NE00241</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9055,21 +9059,17 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>descrição incompleta</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2015NE00223</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>13/2012</t>
-        </is>
-      </c>
+          <t>2015NE00240</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
           <t>03/03/2015</t>
@@ -9085,19 +9085,19 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>OBJETO: SALDO DO 2º TA AO CONTRATO Nº 013/2012 PARA O EXERCÍCIO DE 2015, Contemplando Reajuste de acordo com IGPM. VIGÊNCIA: 02/11/2014 a 02/11/2015 VALOR GLOBAL: R$ 175.477,20 VALOR MENSAL: R$ 14.623</t>
+          <t>vigência incorreta</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2022NE0000045</t>
+          <t>2022NE0000044</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>9764.940000000001</v>
+        <v>4616.08</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9115,19 +9115,19 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>4° T.A CT 03/2017 - PRORROGAÇÃO DA VIGÊNCIA POR MAIS 12(DOZE) MESES, REFERENTE AOS SERVIÇOS DE SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM (SISTEMA DE ACOMPANHAMENT</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SITEMA DE PROTOCOLO PLATAFORMA WEB PARA ATENDER AS DEMANDAS DESTA SEJUSC PELO PERIODO DE 12 MESES</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2022NE0000018</t>
+          <t>2022NE0000037</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>5685.57</v>
+        <v>260580.84</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9145,19 +9145,19 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC.</t>
+          <t xml:space="preserve">Contratação de empresa especializada para a prestação de serviços de rede, acesso a rede do Governo, fornecimento de circuito de transmissão de dados, acesso gerenciado à rede mundial de computadores </t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2022NE0000037</t>
+          <t>2022NE0000018</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>260580.84</v>
+        <v>5685.57</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -9175,19 +9175,19 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada para a prestação de serviços de rede, acesso a rede do Governo, fornecimento de circuito de transmissão de dados, acesso gerenciado à rede mundial de computadores </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2022NE0000044</t>
+          <t>2022NE0000045</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>4616.08</v>
+        <v>9764.940000000001</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SITEMA DE PROTOCOLO PLATAFORMA WEB PARA ATENDER AS DEMANDAS DESTA SEJUSC PELO PERIODO DE 12 MESES</t>
+          <t>4° T.A CT 03/2017 - PRORROGAÇÃO DA VIGÊNCIA POR MAIS 12(DOZE) MESES, REFERENTE AOS SERVIÇOS DE SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM (SISTEMA DE ACOMPANHAMENT</t>
         </is>
       </c>
     </row>
@@ -9242,12 +9242,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2023NE0000902</t>
+          <t>2023NE0000903</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>2069.76</v>
+        <v>7408.9</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9265,19 +9265,19 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2023NE0000903</t>
+          <t>2023NE0000902</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>7408.9</v>
+        <v>2069.76</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -9295,24 +9295,28 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2018NE00204</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr"/>
+          <t>2018NE00201</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>7/2018</t>
+        </is>
+      </c>
       <c r="C305" t="inlineStr">
         <is>
           <t>02/10/2018</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>11296.44</v>
+        <v>3867.09</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9321,7 +9325,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>correção no credor</t>
+          <t>Contratação de empresa em prestação de serviços de sistema SPROWEB. TERMO DE CONTRATO Nº 07/2018</t>
         </is>
       </c>
     </row>
@@ -9354,21 +9358,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2018NE00201</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>7/2018</t>
-        </is>
-      </c>
+          <t>2018NE00204</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
           <t>02/10/2018</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>3867.09</v>
+        <v>11296.44</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Contratação de empresa em prestação de serviços de sistema SPROWEB. TERMO DE CONTRATO Nº 07/2018</t>
+          <t>correção no credor</t>
         </is>
       </c>
     </row>
@@ -9440,12 +9440,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2025NE0000511</t>
+          <t>2025NE0000510</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>15483.52</v>
+        <v>2403.59</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -9463,19 +9463,19 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Contrataçao de Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informa</t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2025NE0000510</t>
+          <t>2025NE0000511</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>2403.59</v>
+        <v>15483.52</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 03.</t>
+          <t>Contrataçao de Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informa</t>
         </is>
       </c>
     </row>
@@ -9530,17 +9530,21 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2017NE00282</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr"/>
+          <t>2017NE00297</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C313" t="inlineStr">
         <is>
           <t>02/05/2017</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>4425.87</v>
+        <v>4775.48</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9549,19 +9553,19 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>(ID-93841) DESENVOLVIMENTO DE WEB SITE, Descrição: Contratação de empresa especializada em desenvolvimento de Website Institucional com sistema de gerenciamento de conteúdo. INFORMAÇÕES ADICIONAIS: Pa</t>
+          <t>(ID-79330) SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB). PA</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2017NE00273</t>
+          <t>2017NE00298</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9570,7 +9574,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>18159.44</v>
+        <v>6640.2</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -9579,19 +9583,19 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>(ID 117367) HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para prestação de serviço de hospedagem do Sistema de Acompanhamento de Mulheres em situação de violênc</t>
+          <t>(ID 59261) SERVIÇOS DE INFORMÁTICA, Descrição: Contratação de empresa para prestação de serviços de informática em geral, conforme projeto básico MARCA: Serviços Eventuais. 1º TA ao CT nº 001/2016-SEJ</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2017NE00298</t>
+          <t>2017NE00273</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9600,7 +9604,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>6640.2</v>
+        <v>18159.44</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -9609,28 +9613,24 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>(ID 59261) SERVIÇOS DE INFORMÁTICA, Descrição: Contratação de empresa para prestação de serviços de informática em geral, conforme projeto básico MARCA: Serviços Eventuais. 1º TA ao CT nº 001/2016-SEJ</t>
+          <t>(ID 117367) HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para prestação de serviço de hospedagem do Sistema de Acompanhamento de Mulheres em situação de violênc</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2017NE00297</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2017NE00282</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
           <t>02/05/2017</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>4775.48</v>
+        <v>4425.87</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>(ID-79330) SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB). PA</t>
+          <t>(ID-93841) DESENVOLVIMENTO DE WEB SITE, Descrição: Contratação de empresa especializada em desenvolvimento de Website Institucional com sistema de gerenciamento de conteúdo. INFORMAÇÕES ADICIONAIS: Pa</t>
         </is>
       </c>
     </row>
@@ -9676,17 +9676,21 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2018NE00229</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr"/>
+          <t>2018NE00221</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C318" t="inlineStr">
         <is>
           <t>02/04/2018</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>220377.33</v>
+        <v>9079.719999999999</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9695,19 +9699,19 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>ANULAÇÃO POR EQUIVOCO NO EMPENHO.</t>
+          <t>EMPENHO CRONOGRAMA MAIO E JUNHO CT 003/2017</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2018NE00222</t>
+          <t>2018NE00218</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9716,7 +9720,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>220377.33</v>
+        <v>2387.74</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -9725,7 +9729,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>EMPENHO CRONOGRAMA ABRIL, MAIO E JUNHO CT 012/2016</t>
+          <t>EMPENHO CRONOGRAMA MAIO E JUNHO CT 002/2016</t>
         </is>
       </c>
     </row>
@@ -9762,12 +9766,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2018NE00218</t>
+          <t>2018NE00222</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9776,7 +9780,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>2387.74</v>
+        <v>220377.33</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -9785,28 +9789,24 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>EMPENHO CRONOGRAMA MAIO E JUNHO CT 002/2016</t>
+          <t>EMPENHO CRONOGRAMA ABRIL, MAIO E JUNHO CT 012/2016</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2018NE00221</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2018NE00229</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr">
         <is>
           <t>02/04/2018</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>9079.719999999999</v>
+        <v>220377.33</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -9815,14 +9815,14 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>EMPENHO CRONOGRAMA MAIO E JUNHO CT 003/2017</t>
+          <t>ANULAÇÃO POR EQUIVOCO NO EMPENHO.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2015NE00285</t>
+          <t>2015NE00284</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>anulaçao para alteração da vigencia.</t>
+          <t xml:space="preserve">3º Termo Aditivo ao Contrato nº 001/2012/SEJUS - Prestação de Serviços de Informática, celebrado entre o Estado do Amazonas, por intermédio da SECRETARIA DE ESTADO DE JUSTIÇA E DIREITOS HUMANOS-SEJUS </t>
         </is>
       </c>
     </row>
@@ -9882,7 +9882,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2015NE00284</t>
+          <t>2015NE00285</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">3º Termo Aditivo ao Contrato nº 001/2012/SEJUS - Prestação de Serviços de Informática, celebrado entre o Estado do Amazonas, por intermédio da SECRETARIA DE ESTADO DE JUSTIÇA E DIREITOS HUMANOS-SEJUS </t>
+          <t>anulaçao para alteração da vigencia.</t>
         </is>
       </c>
     </row>
@@ -9942,12 +9942,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2025NE0000003</t>
+          <t>2025NE0000005</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>8/2022</t>
+          <t>19/2021</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>14817.8</v>
+        <v>4139.52</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -9965,19 +9965,19 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
+          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2025NE0000005</t>
+          <t>2025NE0000003</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>19/2021</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>4139.52</v>
+        <v>14817.8</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web à SEJUSC. TC: 0019/2021 AD: 03.</t>
+          <t xml:space="preserve">Serviços de Hospedagem de Sistemas de Informação, contemplando o Sistema SAM-Sistema de Acompanhamento de Mulheres em situação de violência Domiciliar, manutenção em sistemas de informação do Sistema </t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2020NE00048</t>
+          <t>2020NE00044</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10062,12 +10062,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2020NE00020</t>
+          <t>2020NE00073</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10076,7 +10076,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>9764.940000000001</v>
+        <v>85550.56</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10085,19 +10085,19 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR (SAM), INCLUINDO MANUTENÇÃO E SUPORTE À OPERAÇÃ</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS TÉCNICOS ESPEC. EM TELECOMUNICAÇÕES PARA DISP. DE LINK DE DADOS DEDICADO PARA ACESSO À REDE MUNDIAL DE COMP., DESENVOLVIMENTO DE WEBSITE, EXECUÇÃO DO SIST. PRODAMRH, FORN. DE C</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2020NE00018</t>
+          <t>2020NE00066</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10106,7 +10106,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1785.38</v>
+        <v>11227.05</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -10115,24 +10115,28 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>3º TA AO CT 001/2016 REF A PRESTAÇÃO DE SERVIÇOS EVENTUAIS PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA EXECUÇÃO DE SISTEMA DE PROTOCOLO WEB (SPROWEB)</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2020NE00045</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr"/>
+          <t>2020NE00028</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>34/2016</t>
+        </is>
+      </c>
       <c r="C333" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>230691.71</v>
+        <v>10422.21</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -10141,7 +10145,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO PARA AJUSTES</t>
+          <t>3º TA AO CT Nº 034/2016 REF A PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIDADE DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDE</t>
         </is>
       </c>
     </row>
@@ -10178,21 +10182,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2020NE00028</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>34/2016</t>
-        </is>
-      </c>
+          <t>2020NE00045</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>10422.21</v>
+        <v>230691.71</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -10201,19 +10201,19 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>3º TA AO CT Nº 034/2016 REF A PRESTAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIDADE DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDE</t>
+          <t>ANULAÇÃO DE EMPENHO PARA AJUSTES</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2020NE00066</t>
+          <t>2020NE00018</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>11227.05</v>
+        <v>1785.38</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -10231,19 +10231,19 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA EXECUÇÃO DE SISTEMA DE PROTOCOLO WEB (SPROWEB)</t>
+          <t>3º TA AO CT 001/2016 REF A PRESTAÇÃO DE SERVIÇOS EVENTUAIS PARA ATENDER AS DEMANDAS DA SEJUSC E UNIDADES.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2020NE00073</t>
+          <t>2020NE00020</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>85550.56</v>
+        <v>9764.940000000001</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -10261,14 +10261,14 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS TÉCNICOS ESPEC. EM TELECOMUNICAÇÕES PARA DISP. DE LINK DE DADOS DEDICADO PARA ACESSO À REDE MUNDIAL DE COMP., DESENVOLVIMENTO DE WEBSITE, EXECUÇÃO DO SIST. PRODAMRH, FORN. DE C</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR (SAM), INCLUINDO MANUTENÇÃO E SUPORTE À OPERAÇÃ</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2020NE00044</t>
+          <t>2020NE00048</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10298,12 +10298,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2019NE00037</t>
+          <t>2019NE00028</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10312,7 +10312,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1660.05</v>
+        <v>1193.87</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10321,19 +10321,19 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL (SERVIÇOS EVENTUAIS). CRONOGRAMA: JANEIRO/2019</t>
+          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO WEB (SPROWEB). CRONOGRAMA: JANEIRO/2019</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2019NE00036</t>
+          <t>2019NE00029</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>220377.33</v>
+        <v>4425.87</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET), PARA SEJUSC E DEMAIS UNIDADES. CRONOGRAMA: JANEIRO A MARÇO/2019.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PESSOA JURÍDICA PARA DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM SISTEMA DE GERENCIAMENTO DE CONTEÚDO. CRONOGRAMA: JANEIRO A MARÇO/2019.</t>
         </is>
       </c>
     </row>
@@ -10388,12 +10388,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2019NE00029</t>
+          <t>2019NE00036</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>4425.87</v>
+        <v>220377.33</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10411,19 +10411,19 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PESSOA JURÍDICA PARA DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM SISTEMA DE GERENCIAMENTO DE CONTEÚDO. CRONOGRAMA: JANEIRO A MARÇO/2019.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET), PARA SEJUSC E DEMAIS UNIDADES. CRONOGRAMA: JANEIRO A MARÇO/2019.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2019NE00028</t>
+          <t>2019NE00037</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1193.87</v>
+        <v>1660.05</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10441,19 +10441,19 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO WEB (SPROWEB). CRONOGRAMA: JANEIRO/2019</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL (SERVIÇOS EVENTUAIS). CRONOGRAMA: JANEIRO/2019</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2019NE00009</t>
+          <t>2019NE00011</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>7/2018</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>32081.46</v>
+        <v>3742.35</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -10471,19 +10471,19 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prestação de serviços de firewall, prodam Rh, internet, link e gestor de conteúdo. 2º Termo aditivo ao contrato Nº07/2016</t>
+          <t>Contratação de empresa especializada na prestação de serviços de SPROWEB CT Nº 07/2018</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2019NE00011</t>
+          <t>2019NE00009</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>7/2018</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>3742.35</v>
+        <v>32081.46</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10501,19 +10501,19 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de SPROWEB CT Nº 07/2018</t>
+          <t>Contratação de empresa especializada em prestação de serviços de firewall, prodam Rh, internet, link e gestor de conteúdo. 2º Termo aditivo ao contrato Nº07/2016</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2018NE00027</t>
+          <t>2018NE00067</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10522,7 +10522,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>5418.24</v>
+        <v>1660.05</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -10531,19 +10531,19 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>5 TA AO CT 09/2013 Contratação de prestação de serviços SPROWEB</t>
+          <t>1º Termo Aditivo ao Contrato Nº 001/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Serviços Eventuais. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2018NE00070</t>
+          <t>2018NE00069</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>8851.74</v>
+        <v>9079.719999999999</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CT Nº 034/2016-SEJUSC; OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL DA SEJUSC. VIGÊNCIA: 04/08/2017 A 03/08/2018. VALOR GLOBAL: R$ 17.70</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM-SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR.</t>
         </is>
       </c>
     </row>
@@ -10598,12 +10598,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2018NE00069</t>
+          <t>2018NE00070</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>9079.719999999999</v>
+        <v>8851.74</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SISTEMAS DE INFORMAÇÃO COMPREENDENDO A HOSPEDAGEM E A MANUTENÇÃO DO SISTEMA SAM-SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR.</t>
+          <t>1º TERMO ADITIVO AO CT Nº 034/2016-SEJUSC; OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL DA SEJUSC. VIGÊNCIA: 04/08/2017 A 03/08/2018. VALOR GLOBAL: R$ 17.70</t>
         </is>
       </c>
     </row>
@@ -10658,12 +10658,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2018NE00067</t>
+          <t>2018NE00027</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1660.05</v>
+        <v>5418.24</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10681,19 +10681,19 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato Nº 001/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Serviços Eventuais. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
+          <t>5 TA AO CT 09/2013 Contratação de prestação de serviços SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2017NE00028</t>
+          <t>2017NE00027</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -10702,7 +10702,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1500</v>
+        <v>1097.41</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -10711,19 +10711,19 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM INFORMÁTICA DE FORMA EVENTUAL.</t>
+          <t>CONTRATAÇÃO DO SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB(SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2017NE00025</t>
+          <t>2017NE00026</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -10732,7 +10732,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>5901.16</v>
+        <v>206616.39</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO FORNECIMENTO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A SEJUSC.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA(HARDWARE E SOFTWARE), SERVIÇOS DE REDE COMPREENDENDO A DISP. DE ACESSO À REDE DE GOVERNO COM O FORNECIMENTO DE LINKS SEGURO</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2017NE00004</t>
+          <t>2017NE00025</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>2709.12</v>
+        <v>5901.16</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -10801,19 +10801,19 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviços de licença de uso de sistema de informação, Sistema de Protocolo em Plataforma web (SPROWEB). DISPENSA DE LICITAÇÃO Nº 04/2013</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO FORNECIMENTO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A SEJUSC.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2017NE00002</t>
+          <t>2017NE00028</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>41861.12</v>
+        <v>1500</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -10831,19 +10831,19 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviço de acesso à rede de internet e computador central, serviço de processamento do sistema CFPP e serviços eventuais de informatica. Dispensa de Licitação RDL Nº 02/201</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS TÉCNICOS EM INFORMÁTICA DE FORMA EVENTUAL.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2017NE00026</t>
+          <t>2017NE00002</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>206616.39</v>
+        <v>41861.12</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -10861,19 +10861,19 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA(HARDWARE E SOFTWARE), SERVIÇOS DE REDE COMPREENDENDO A DISP. DE ACESSO À REDE DE GOVERNO COM O FORNECIMENTO DE LINKS SEGURO</t>
+          <t>Contratação de prestação de serviço de acesso à rede de internet e computador central, serviço de processamento do sistema CFPP e serviços eventuais de informatica. Dispensa de Licitação RDL Nº 02/201</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2017NE00027</t>
+          <t>2017NE00004</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1097.41</v>
+        <v>2709.12</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -10891,19 +10891,19 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO SERVIÇO DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB(SPROWEB).</t>
+          <t>Contratação de prestação de serviços de licença de uso de sistema de informação, Sistema de Protocolo em Plataforma web (SPROWEB). DISPENSA DE LICITAÇÃO Nº 04/2013</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2014NE00035</t>
+          <t>2014NE00133</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>1/2012</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>6750</v>
+        <v>13953.36</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -10921,19 +10921,19 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Contrato No. 9/2013 - Sistema de Protocolo em plataforma Web - SPROWEB</t>
+          <t>Contrato No. 1/2012 - Hospedagem e confeccão de website</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2014NE00130</t>
+          <t>2014NE00125</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>13/2012</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10942,7 +10942,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>120000</v>
+        <v>48000</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -10951,19 +10951,19 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Contrato No. 13/2012 - SPEC-Sistema Penit. e Exec. Criminais</t>
+          <t>Contrato No. 5/2014 - Serviços Eventuais de Informatica</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2014NE00056</t>
+          <t>2014NE00059</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2/2011</t>
+          <t>7/2010</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>10000</v>
+        <v>80392.2</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -10981,19 +10981,19 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Contrato No. 2/2011 - Sistema de PROTOCOLO SPRO.Web</t>
+          <t>Contrato No. 7/2010 - Acesso Computador Central 3 Mbps /Internet - velocidade 2 Mbps</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2014NE00059</t>
+          <t>2014NE00056</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>7/2010</t>
+          <t>2/2011</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>80392.2</v>
+        <v>10000</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -11011,19 +11011,19 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Contrato No. 7/2010 - Acesso Computador Central 3 Mbps /Internet - velocidade 2 Mbps</t>
+          <t>Contrato No. 2/2011 - Sistema de PROTOCOLO SPRO.Web</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2014NE00015</t>
+          <t>2014NE00130</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>3/2011</t>
+          <t>13/2012</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>92779.03999999999</v>
+        <v>120000</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Contrato No. 3/2011 - Computador Central 3 Mbps/Internet/CFPP/Serviços Eventuais</t>
+          <t>Contrato No. 13/2012 - SPEC-Sistema Penit. e Exec. Criminais</t>
         </is>
       </c>
     </row>
@@ -11078,12 +11078,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2014NE00125</t>
+          <t>2014NE00015</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>3/2011</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>48000</v>
+        <v>92779.03999999999</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -11101,19 +11101,19 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Contrato No. 5/2014 - Serviços Eventuais de Informatica</t>
+          <t>Contrato No. 3/2011 - Computador Central 3 Mbps/Internet/CFPP/Serviços Eventuais</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2014NE00133</t>
+          <t>2014NE00035</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>1/2012</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>13953.36</v>
+        <v>6750</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11131,19 +11131,19 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Contrato No. 1/2012 - Hospedagem e confeccão de website</t>
+          <t>Contrato No. 9/2013 - Sistema de Protocolo em plataforma Web - SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2016NE00770</t>
+          <t>2016NE00771</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>543.0599999999999</v>
+        <v>1097.41</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -11161,19 +11161,19 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>CONTRATO DE EMPRESA ESPECIALIZADA NA PRESTACAO DE SERVICOS DE HOSPEDAGEM PARA WEBSITE PARA ATENDER AS NECESSIDADES DA SEJUSC NO MES DEZEMBRO/2016 CT 07/2016-SEJUSC</t>
+          <t>CONTRATO DE EMPRESA ESPECIALIZADA NA PRESTACAO DE SERVICOS DE CESSAO DE USO DO PROGRAMA SPROWEB PARA ACOMPANHAR, CONTROLAR TODOS OS REGISTROS DE DOCUMENTOS. DEZEMBRO/2016 CT 02/2016-SEJUSC</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2016NE00768</t>
+          <t>2016NE00767</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -11182,7 +11182,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1475.29</v>
+        <v>68872.13</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>CONTRATO DE EMPRESA ESPECIALIZADA EM DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM SISTEMA DE GERENCIAMENTO DE CONTEUDO PARA ATENDER AS NECESSIDADES DA SEJUSC NO MES DEZEMBRO/2016 CT 34/2016-SEJUSC</t>
+          <t>SERVICOS DE ACESSO A INTERNET A REDE MUNDIAL DE COMPUTADORES NO MES DEZEMBRO/2016 CT 12/2016-SEJUSC</t>
         </is>
       </c>
     </row>
@@ -11228,12 +11228,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2016NE00767</t>
+          <t>2016NE00768</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>68872.13</v>
+        <v>1475.29</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -11251,19 +11251,19 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>SERVICOS DE ACESSO A INTERNET A REDE MUNDIAL DE COMPUTADORES NO MES DEZEMBRO/2016 CT 12/2016-SEJUSC</t>
+          <t>CONTRATO DE EMPRESA ESPECIALIZADA EM DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM SISTEMA DE GERENCIAMENTO DE CONTEUDO PARA ATENDER AS NECESSIDADES DA SEJUSC NO MES DEZEMBRO/2016 CT 34/2016-SEJUSC</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2016NE00771</t>
+          <t>2016NE00770</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1097.41</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11281,14 +11281,14 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>CONTRATO DE EMPRESA ESPECIALIZADA NA PRESTACAO DE SERVICOS DE CESSAO DE USO DO PROGRAMA SPROWEB PARA ACOMPANHAR, CONTROLAR TODOS OS REGISTROS DE DOCUMENTOS. DEZEMBRO/2016 CT 02/2016-SEJUSC</t>
+          <t>CONTRATO DE EMPRESA ESPECIALIZADA NA PRESTACAO DE SERVICOS DE HOSPEDAGEM PARA WEBSITE PARA ATENDER AS NECESSIDADES DA SEJUSC NO MES DEZEMBRO/2016 CT 07/2016-SEJUSC</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2019NE00611</t>
+          <t>2019NE00612</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -11298,7 +11298,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>299.17</v>
+        <v>6203.97</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2019NE00613</t>
+          <t>2019NE00614</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1660.05</v>
+        <v>2979.88</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2019NE00614</t>
+          <t>2019NE00613</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>2979.88</v>
+        <v>1660.05</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2019NE00612</t>
+          <t>2019NE00611</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>6203.97</v>
+        <v>299.17</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2017NE00368</t>
+          <t>2017NE00358</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11415,17 +11415,21 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Contratação de empresa em prestação de serviços de link de comunicação, sistema de transmissão de dados, execução de sistema de informação, desenvolvimento de website e segurança da informação. 1º TER</t>
+          <t xml:space="preserve">Contratação de empresa em prestação de serviços de link de comunicação, sistema de transmissão de dados, execução de sistema de informação, desenvolvimento de website e segurança da informação. 1º TA </t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2017NE00365</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr"/>
+          <t>2017NE00355</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>9/2013</t>
+        </is>
+      </c>
       <c r="C377" t="inlineStr">
         <is>
           <t>01/11/2017</t>
@@ -11441,24 +11445,28 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA CORREÇÃO NA DESCRIÇÃO.</t>
+          <t>Contratação de empresa em prestação de serviços SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2017NE00367</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr"/>
+          <t>2017NE00366</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>9/2013</t>
+        </is>
+      </c>
       <c r="C378" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>10255.92</v>
+        <v>677.28</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -11467,28 +11475,24 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA CORREÇÃO NA DESCRIÇÃO</t>
+          <t>Contratação de empresa em prestação de serviços SPROWEB. 5º TERMO ADITIVO AO CONTRATO Nº 09/2013</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2017NE00366</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>9/2013</t>
-        </is>
-      </c>
+          <t>2017NE00367</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>677.28</v>
+        <v>10255.92</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -11497,21 +11501,17 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Contratação de empresa em prestação de serviços SPROWEB. 5º TERMO ADITIVO AO CONTRATO Nº 09/2013</t>
+          <t>ANULAÇÃO TOTAL PARA CORREÇÃO NA DESCRIÇÃO</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2017NE00355</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>9/2013</t>
-        </is>
-      </c>
+          <t>2017NE00365</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
         <is>
           <t>01/11/2017</t>
@@ -11527,14 +11527,14 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Contratação de empresa em prestação de serviços SPROWEB.</t>
+          <t>ANULAÇÃO TOTAL PARA CORREÇÃO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2017NE00358</t>
+          <t>2017NE00368</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11557,19 +11557,19 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa em prestação de serviços de link de comunicação, sistema de transmissão de dados, execução de sistema de informação, desenvolvimento de website e segurança da informação. 1º TA </t>
+          <t>Contratação de empresa em prestação de serviços de link de comunicação, sistema de transmissão de dados, execução de sistema de informação, desenvolvimento de website e segurança da informação. 1º TER</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2016NE00721</t>
+          <t>2016NE00722</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1500</v>
+        <v>1475.29</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -11587,19 +11587,19 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTACAO DE SERVIÇOS DE INFORMATICA EM GERAL, CONFORME PROJETO BASICO PARA ATENDER AS NECESSIDADES DA SEJUSC. CT 001/2016-SEJUSC</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM SISTEMA DE GERENCIAMENTO DE CONTEUDO. CT 34/2016-SEJUSC</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2016NE00723</t>
+          <t>2016NE00719</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11608,7 +11608,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>68872.13</v>
+        <v>1097.41</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET) CONFORME DISCRIMINADO EM PROJETO BASICO. CT 012/2016</t>
+          <t>SERVIÇOS DE PROCESSAMENTOS DE DADOS, ESPECIALIZADO EM CESSAO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZACAO DO SISTEMA PROTOCOLO WEB SPROWEB PARA ATENDER AS NECESSIDADES DA SEJUSC. CT 02/2016-</t>
         </is>
       </c>
     </row>
@@ -11654,12 +11654,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2016NE00719</t>
+          <t>2016NE00723</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1097.41</v>
+        <v>68872.13</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -11677,19 +11677,19 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTOS DE DADOS, ESPECIALIZADO EM CESSAO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZACAO DO SISTEMA PROTOCOLO WEB SPROWEB PARA ATENDER AS NECESSIDADES DA SEJUSC. CT 02/2016-</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET) CONFORME DISCRIMINADO EM PROJETO BASICO. CT 012/2016</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2016NE00722</t>
+          <t>2016NE00721</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1475.29</v>
+        <v>1500</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -11707,19 +11707,19 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM SISTEMA DE GERENCIAMENTO DE CONTEUDO. CT 34/2016-SEJUSC</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTACAO DE SERVIÇOS DE INFORMATICA EM GERAL, CONFORME PROJETO BASICO PARA ATENDER AS NECESSIDADES DA SEJUSC. CT 001/2016-SEJUSC</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2016NE00260</t>
+          <t>2016NE00258</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>677.28</v>
+        <v>10255.92</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -11737,19 +11737,19 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t xml:space="preserve">4º TERMO ADITIVO AO CONTRATO Nº 09/2013, VIGÊNCIA: 27/09/2016 A 26/09/2017 VALOR GLOBAL: R$ 8.127,36 VALOR MENSAL: R$ 677,28 EMPENHAR ATÉ FINAL DO EXERCÍCIO R$677,28 EMPENHAR NO EXERCÍCIO SEGUINTE R$ </t>
+          <t>CONTRATO Nº 07/2016 VIGÊNCIA 01/09/2016 A 31/08/2017 VALOR GLOBAL R$ 124.745,92 VALOR MENSAL R$ 10.255,92 FUNDAMENTAÇÃO LEGAL: DISPENSA DE LICITAÇÃO RDL Nº 02/2016, PORTARIA DE LICITAÇÃO Nº 14 GSEPED,</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2016NE00258</t>
+          <t>2016NE00260</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11758,7 +11758,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>10255.92</v>
+        <v>677.28</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -11767,14 +11767,14 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>CONTRATO Nº 07/2016 VIGÊNCIA 01/09/2016 A 31/08/2017 VALOR GLOBAL R$ 124.745,92 VALOR MENSAL R$ 10.255,92 FUNDAMENTAÇÃO LEGAL: DISPENSA DE LICITAÇÃO RDL Nº 02/2016, PORTARIA DE LICITAÇÃO Nº 14 GSEPED,</t>
+          <t xml:space="preserve">4º TERMO ADITIVO AO CONTRATO Nº 09/2013, VIGÊNCIA: 27/09/2016 A 26/09/2017 VALOR GLOBAL: R$ 8.127,36 VALOR MENSAL: R$ 677,28 EMPENHAR ATÉ FINAL DO EXERCÍCIO R$677,28 EMPENHAR NO EXERCÍCIO SEGUINTE R$ </t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2017NE00289</t>
+          <t>2017NE00294</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -11788,7 +11788,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>464.21</v>
+        <v>750</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -11797,19 +11797,19 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, execução de sistema cad/folha.pagto, nota fiscal nº 16390 de 28/10/2015 (outubro), Termo Contrato nº 03/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, serviços eventuais, nota fiscal nº 16716 de 26/11/2015 (agosto 2014), Termo Contrato nº 03/2011</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2017NE00290</t>
+          <t>2017NE00287</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>3/2011</t>
+          <t>10/2011</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>458.1</v>
+        <v>366.11</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -11827,14 +11827,14 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, execução de sistema cad/folha.pagto, nota fiscal nº 16701 de 25/11/2015 (novembro), Termo Contrato nº 03/2011</t>
+          <t>Pagamento de serviços de processamentos de dados,desenvolvimento, confeção e implantação de web site, nota fiscal nº 15356 de 14/08/2015 (agosto), 3º Termo Aditivo ao cont. 10/2011</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2017NE00284</t>
+          <t>2017NE00286</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -11857,19 +11857,19 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, sistema de protocolo em plataforma web (SPROWEB), nota fiscal nº 16329 de 23/10/2015 (outubro), 3º Termo Aditivo ao cont. 09/2013,</t>
+          <t>Pagamento de serviços de processamentos de dados, sistema de protocolo em plataforma web (SPROWEB), nota fiscal nº 16993 de 15/15/2015 (dezembro), 3º Termo Aditivo ao cont. 09/2013,</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2017NE00285</t>
+          <t>2017NE00295</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>9/2013</t>
+          <t>3/2011</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>677.28</v>
+        <v>750</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -11887,19 +11887,19 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, sistema de protocolo em plataforma web (SPROWEB), nota fiscal nº 16622 de 17/11/2015 (novembro), 3º Termo Aditivo ao cont. 09/2013,</t>
+          <t>Pagamento de serviços de processamentos de dados, serviços eventuais, nota fiscal nº 16710 de 26/11/2015 (fevereiro 2014), Termo Contrato nº 03/2011</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2017NE00292</t>
+          <t>2017NE00293</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>10/2011</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11908,7 +11908,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>366.11</v>
+        <v>522.72</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -11917,14 +11917,14 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados,desenvolvimento, confeção e implantação de web site, nota fiscal nº 17023 de 16/12/2015 (dezembro), 3º Termo Aditivo ao cont. 10/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, execução de sistema de recursos humanos e folha, nota fiscal nº 21255 de 19/12/2016 (dezembro), Termo Contrato nº 07/2016</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2017NE00291</t>
+          <t>2017NE00288</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11947,14 +11947,14 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, circuito ponto a ponto de 10mbps, fibra ótica, acesso a internet e equipamento firewall, nota fiscal nº 16859 de 02/12/2015 (dezembro), Termo Contrato</t>
+          <t>Pagamento de serviços de processamentos de dados, acesso gerenciado a rede mundial, circuito ponto a ponto, acesso a internet e equipamento firewall, nota fiscal nº 16576 de 10/11/2015 (novembro) Term</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2017NE00288</t>
+          <t>2017NE00291</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -11977,19 +11977,19 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, acesso gerenciado a rede mundial, circuito ponto a ponto, acesso a internet e equipamento firewall, nota fiscal nº 16576 de 10/11/2015 (novembro) Term</t>
+          <t>Pagamento de serviços de processamentos de dados, circuito ponto a ponto de 10mbps, fibra ótica, acesso a internet e equipamento firewall, nota fiscal nº 16859 de 02/12/2015 (dezembro), Termo Contrato</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2017NE00293</t>
+          <t>2017NE00292</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>10/2011</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11998,7 +11998,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>522.72</v>
+        <v>366.11</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -12007,19 +12007,19 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, execução de sistema de recursos humanos e folha, nota fiscal nº 21255 de 19/12/2016 (dezembro), Termo Contrato nº 07/2016</t>
+          <t>Pagamento de serviços de processamentos de dados,desenvolvimento, confeção e implantação de web site, nota fiscal nº 17023 de 16/12/2015 (dezembro), 3º Termo Aditivo ao cont. 10/2011</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2017NE00295</t>
+          <t>2017NE00285</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>3/2011</t>
+          <t>9/2013</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>750</v>
+        <v>677.28</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -12037,14 +12037,14 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, serviços eventuais, nota fiscal nº 16710 de 26/11/2015 (fevereiro 2014), Termo Contrato nº 03/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, sistema de protocolo em plataforma web (SPROWEB), nota fiscal nº 16622 de 17/11/2015 (novembro), 3º Termo Aditivo ao cont. 09/2013,</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2017NE00286</t>
+          <t>2017NE00284</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -12067,19 +12067,19 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, sistema de protocolo em plataforma web (SPROWEB), nota fiscal nº 16993 de 15/15/2015 (dezembro), 3º Termo Aditivo ao cont. 09/2013,</t>
+          <t>Pagamento de serviços de processamentos de dados, sistema de protocolo em plataforma web (SPROWEB), nota fiscal nº 16329 de 23/10/2015 (outubro), 3º Termo Aditivo ao cont. 09/2013,</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2017NE00287</t>
+          <t>2017NE00290</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>10/2011</t>
+          <t>3/2011</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>366.11</v>
+        <v>458.1</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -12097,14 +12097,14 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados,desenvolvimento, confeção e implantação de web site, nota fiscal nº 15356 de 14/08/2015 (agosto), 3º Termo Aditivo ao cont. 10/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, execução de sistema cad/folha.pagto, nota fiscal nº 16701 de 25/11/2015 (novembro), Termo Contrato nº 03/2011</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2017NE00294</t>
+          <t>2017NE00289</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -12118,7 +12118,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>750</v>
+        <v>464.21</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Pagamento de serviços de processamentos de dados, serviços eventuais, nota fiscal nº 16716 de 26/11/2015 (agosto 2014), Termo Contrato nº 03/2011</t>
+          <t>Pagamento de serviços de processamentos de dados, execução de sistema cad/folha.pagto, nota fiscal nº 16390 de 28/10/2015 (outubro), Termo Contrato nº 03/2011</t>
         </is>
       </c>
     </row>
@@ -12164,12 +12164,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2019NE00317</t>
+          <t>2019NE00318</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>5356.14</v>
+        <v>235252.38</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12187,19 +12187,19 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t xml:space="preserve">59261 - SERVIÇOS DE INFORMÁTICA, Descrição: SERVIÇOS DE INFORMÁTICA, Descrição: Contratação de empresa para prestação de serviços de informática em geral, conforme projeto básico MARCA: null 3º TERMO </t>
+          <t>46139 - SERVIÇOS DE ACESSO À INTERNET, Descrição: SERVIÇOS DE ACESSO À INTERNET, Descrição: contratação de empresa especializada na prestação de serviço de acesso à rede mundial de computadores (Inter</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2019NE00320</t>
+          <t>2019NE00319</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>3852</v>
+        <v>14647.41</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>79330 - SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGARAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA</t>
+          <t>117367 - HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, : HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para prestação de serviço de hospedagem do Sistema de Acompanhament</t>
         </is>
       </c>
     </row>
@@ -12254,12 +12254,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2019NE00319</t>
+          <t>2019NE00320</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>14647.41</v>
+        <v>3852</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -12277,19 +12277,19 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>117367 - HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, : HOSPEDAGEM DE SISTEMA DE INFORMAÇÃO, Descrição: Contratação de empresa especializada para prestação de serviço de hospedagem do Sistema de Acompanhament</t>
+          <t>79330 - SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGARAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2019NE00318</t>
+          <t>2019NE00317</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>235252.38</v>
+        <v>5356.14</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -12307,19 +12307,19 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>46139 - SERVIÇOS DE ACESSO À INTERNET, Descrição: SERVIÇOS DE ACESSO À INTERNET, Descrição: contratação de empresa especializada na prestação de serviço de acesso à rede mundial de computadores (Inter</t>
+          <t xml:space="preserve">59261 - SERVIÇOS DE INFORMÁTICA, Descrição: SERVIÇOS DE INFORMÁTICA, Descrição: Contratação de empresa para prestação de serviços de informática em geral, conforme projeto básico MARCA: null 3º TERMO </t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2016NE00420</t>
+          <t>2016NE00422</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>3292.23</v>
+        <v>1629.18</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -12337,19 +12337,19 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>TC 002/2016-SEJUSC. SERVIÇOS DE PROCESSAMENTOS DE DADOS, SISTEMA DE PROTOCOLO WEB SPROWEB PARA ATENDER AS NECESSIDADES DA SEJUSC.</t>
+          <t>CT 007/2016, CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM PARA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2016NE00421</t>
+          <t>2016NE00419</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>4500</v>
+        <v>206616.39</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -12367,19 +12367,19 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>TC 001/2016, CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL.</t>
+          <t>CT 012/2016 SEJUSC, SERVIÇOS DE ACESSO A INTERNET A REDE MUNDIAL DE COMPUTADORES PARA ATENDER AS NECESSIDADES DA SEJUSC.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2016NE00419</t>
+          <t>2016NE00421</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -12388,7 +12388,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>206616.39</v>
+        <v>4500</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -12397,19 +12397,19 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>CT 012/2016 SEJUSC, SERVIÇOS DE ACESSO A INTERNET A REDE MUNDIAL DE COMPUTADORES PARA ATENDER AS NECESSIDADES DA SEJUSC.</t>
+          <t>TC 001/2016, CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2016NE00422</t>
+          <t>2016NE00420</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -12418,7 +12418,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1629.18</v>
+        <v>3292.23</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12427,19 +12427,19 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>CT 007/2016, CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE HOSPEDAGEM PARA WEBSITE.</t>
+          <t>TC 002/2016-SEJUSC. SERVIÇOS DE PROCESSAMENTOS DE DADOS, SISTEMA DE PROTOCOLO WEB SPROWEB PARA ATENDER AS NECESSIDADES DA SEJUSC.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2019NE00056</t>
+          <t>2019NE00156</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>7/2018</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>3742.35</v>
+        <v>4425.87</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -12457,19 +12457,19 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de SPROWEB</t>
+          <t>CONTRATAÇÃO EMPRESA PESSOA JURÍDICA PARA DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM SISTEMA DE GERENCIAMENTO DE CONTEÚDO.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2019NE00154</t>
+          <t>2019NE00155</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>3852</v>
+        <v>5356.14</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO WEB (SPROWEB) MESES: ABRIL A JUNHO/2019 CT 02/2016</t>
+          <t>PRESTAÇÃO DE SERVIÇOS EVENTUAIS EM GERAL. MESES: ABRIL, MAIO E JUNHO/2019 CT 01/2016</t>
         </is>
       </c>
     </row>
@@ -12524,12 +12524,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2019NE00155</t>
+          <t>2019NE00154</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12538,7 +12538,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>5356.14</v>
+        <v>3852</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -12547,19 +12547,19 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS EVENTUAIS EM GERAL. MESES: ABRIL, MAIO E JUNHO/2019 CT 01/2016</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO WEB (SPROWEB) MESES: ABRIL A JUNHO/2019 CT 02/2016</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2019NE00156</t>
+          <t>2019NE00055</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>4425.87</v>
+        <v>32081.46</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -12577,19 +12577,19 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO EMPRESA PESSOA JURÍDICA PARA DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL COM SISTEMA DE GERENCIAMENTO DE CONTEÚDO.</t>
+          <t>Contratação de empresa especializada em prestação de serviços de firewall, prodam Rh, internet, link e gestor de conteúdo.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2019NE00055</t>
+          <t>2019NE00056</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>7/2018</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>32081.46</v>
+        <v>3742.35</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prestação de serviços de firewall, prodam Rh, internet, link e gestor de conteúdo.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de SPROWEB</t>
         </is>
       </c>
     </row>
@@ -12734,21 +12734,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2018NE00114</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2018NE00088</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
       <c r="C421" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>3581.61</v>
+        <v>1660.05</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -12757,14 +12753,14 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO Nº 002/2016-SEJUSC; OBJETO: PRORROGAÇÃO DE PRAZO, PLATAFORMA SPROWEB. VIGÊNCIA: 01/02/18 A 31/01/2019; VALOR GLOBAL R$ 14.326,47; VALOR MENSAL R$ 1.193,87; FUNDAMENTO LEGA</t>
+          <t>ANULAÇÃO PARA AJUSTE DA NATUREZA DE DESPESA.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2018NE00110</t>
+          <t>2018NE00115</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -12778,7 +12774,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>1660.05</v>
+        <v>4980.15</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -12787,19 +12783,19 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato Nº 001/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Serviços Eventuais. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
+          <t>2º TERMO ADITIVO AO CONTRATO Nº 001/2016-SEJUSC; OBJETO: PRORROGAÇÃO DE PRAZO, SERVIÇOS EVENTUAIS. VIGÊNCIA: 01/02/2018 A 31/01/2019; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2018NE00111</t>
+          <t>2018NE00113</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>34/2016</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -12808,7 +12804,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>220377.33</v>
+        <v>8851.74</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -12817,28 +12813,24 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO Nº 012/2016-SEJUSC VIGÊNCIA: 07/04/17 A 06/04/18. VALOR GLOBAL: R$ 881.509,32. VALOR MENSAL: R$ 73.459,11. FUND. LEGAL: DISPENSA DE LICITAÇÃO COM BASE NA PORTARIA DE DISPE</t>
+          <t>1º TERMO ADITIVO AO CT Nº 034/2016-SEJUSC; OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL DA SEJUSC. VIGÊNCIA: 04/08/2017 A 03/08/2018. VALOR GLOBAL: R$ 17.70</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2018NE00112</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2018NE00089</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
       <c r="C424" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>9079.719999999999</v>
+        <v>1193.87</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -12847,28 +12839,24 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>CONTRATO Nº 003/2017-SEJUSC; OBJETO: SISTEMA DE INFORMAÇÃO ¿ SAM (SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR; VIGÊNCIA: 01/03/2017 A 28/02/2018; VALOR GLOBAL: R$ 54.478,</t>
+          <t>ANULAÇÃO PARA AJUSTE DA NATUREZA DE DESPESA.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2018NE00109</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2018NE00090</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1193.87</v>
+        <v>8851.74</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -12877,24 +12865,28 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato Nº 002/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Plataforma Sproweb. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 14.326,47; VALOR MENSAL R$ 1.193,87; FUNDAMENTO LE</t>
+          <t>ANULAÇÃO PARA AJUSTE DA NATUREZA DE DESPESA.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2018NE00090</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr"/>
+          <t>2018NE00109</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C426" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>8851.74</v>
+        <v>1193.87</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -12903,24 +12895,28 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARA AJUSTE DA NATUREZA DE DESPESA.</t>
+          <t>1º Termo Aditivo ao Contrato Nº 002/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Plataforma Sproweb. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 14.326,47; VALOR MENSAL R$ 1.193,87; FUNDAMENTO LE</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2018NE00089</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr"/>
+          <t>2018NE00112</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C427" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1193.87</v>
+        <v>9079.719999999999</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -12929,19 +12925,19 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARA AJUSTE DA NATUREZA DE DESPESA.</t>
+          <t>CONTRATO Nº 003/2017-SEJUSC; OBJETO: SISTEMA DE INFORMAÇÃO ¿ SAM (SISTEMA DE ACOMPANHAMENTO DE MULHERES EM SITUAÇÃO DE VIOLÊNCIA DOMICILIAR; VIGÊNCIA: 01/03/2017 A 28/02/2018; VALOR GLOBAL: R$ 54.478,</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2018NE00113</t>
+          <t>2018NE00111</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>34/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -12950,7 +12946,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>8851.74</v>
+        <v>220377.33</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -12959,14 +12955,14 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CT Nº 034/2016-SEJUSC; OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO DESENVOLVIMENTO DE WEBSITE INSTITUCIONAL DA SEJUSC. VIGÊNCIA: 04/08/2017 A 03/08/2018. VALOR GLOBAL: R$ 17.70</t>
+          <t>1º TERMO ADITIVO AO CONTRATO Nº 012/2016-SEJUSC VIGÊNCIA: 07/04/17 A 06/04/18. VALOR GLOBAL: R$ 881.509,32. VALOR MENSAL: R$ 73.459,11. FUND. LEGAL: DISPENSA DE LICITAÇÃO COM BASE NA PORTARIA DE DISPE</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2018NE00115</t>
+          <t>2018NE00110</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -12980,7 +12976,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>4980.15</v>
+        <v>1660.05</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -12989,24 +12985,28 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO Nº 001/2016-SEJUSC; OBJETO: PRORROGAÇÃO DE PRAZO, SERVIÇOS EVENTUAIS. VIGÊNCIA: 01/02/2018 A 31/01/2019; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
+          <t>1º Termo Aditivo ao Contrato Nº 001/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Serviços Eventuais. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2018NE00088</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr"/>
+          <t>2018NE00114</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C430" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1660.05</v>
+        <v>3581.61</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -13015,17 +13015,21 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARA AJUSTE DA NATUREZA DE DESPESA.</t>
+          <t>2º TERMO ADITIVO AO CONTRATO Nº 002/2016-SEJUSC; OBJETO: PRORROGAÇÃO DE PRAZO, PLATAFORMA SPROWEB. VIGÊNCIA: 01/02/18 A 31/01/2019; VALOR GLOBAL R$ 14.326,47; VALOR MENSAL R$ 1.193,87; FUNDAMENTO LEGA</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2017NE00106</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr"/>
+          <t>2017NE00107</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1/2016</t>
+        </is>
+      </c>
       <c r="C431" t="inlineStr">
         <is>
           <t>01/02/2017</t>
@@ -13041,19 +13045,19 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>ANULAÇÃO POR EQUIVOCO NA DESCRIÇÃO.</t>
+          <t>1º Termo Aditivo ao Contrato Nº 001/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Serviços Eventuais. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2017NE00070</t>
+          <t>2017NE00071</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -13062,7 +13066,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>4980.15</v>
+        <v>3581.61</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -13071,19 +13075,19 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato Nº 001/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Serviços Eventuais. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
+          <t>1º Termo Aditivo ao Contrato Nº 002/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Plataforma Sproweb. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 14.326,47; VALOR MENSAL R$ 1.193,87; FUNDAMENTO LE</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2017NE00071</t>
+          <t>2017NE00070</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -13092,7 +13096,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>3581.61</v>
+        <v>4980.15</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -13101,21 +13105,17 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato Nº 002/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Plataforma Sproweb. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 14.326,47; VALOR MENSAL R$ 1.193,87; FUNDAMENTO LE</t>
+          <t>1º Termo Aditivo ao Contrato Nº 001/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Serviços Eventuais. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2017NE00107</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>1/2016</t>
-        </is>
-      </c>
+          <t>2017NE00106</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr">
         <is>
           <t>01/02/2017</t>
@@ -13131,7 +13131,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato Nº 001/2016-SEJUSC; OBJETO: Prorrogação de Prazo, Serviços Eventuais. VIGÊNCIA: 01/02/2017 a 31/01/2018; VALOR GLOBAL R$ 19.920,60; VALOR MENSAL R$ 1.660,05; FUNDAMENTO LE</t>
+          <t>ANULAÇÃO POR EQUIVOCO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SEJUSC/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEJUSC/dossie.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
